--- a/indicator-performance-table.xlsx
+++ b/indicator-performance-table.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="194">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -525,6 +525,75 @@
   </si>
   <si>
     <t xml:space="preserve">However, trust in the NI Assembly was higher in 2024 than in 2022 and 2023.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">During 2024/25, half (51.0 per cent) of the household waste collected by NI councils was reused, recycled or composted. The household waste recycling rate increased from 27.7 per cent in 2006/07 to a high of 51.9 per cent in 2019/20.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">There were a number of significant changes to the survey methodology from 2020, due to the Covid-19 pandemic. In addition to these changes, the impact of the pandemic and the resultant introduction of new public health regulations, guidance and advice may have also fundamentally changed peoples’ behaviour and attitudes.  While 2020 to 2023 results can be compared to each other, care should be taken in reaching any conclusions based on these data and comparisons to previous years. The base year for this indicator has been set to 2022.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This means that more adults in 2024 feel their cultural identity is respected by society than in 2020.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2018-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">There was a significant decrease in female healthy life expectancy between 2018-20 (62.1 years) and 2022-24 (60.2 years).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">There was no significant change in male healthy life expectancy between 2018-20 (60.1 years) and 2022-24 (59.3 years).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In 2023/24, around a fifth (19%) of respondents had a high GHQ12 score, which could indicate a mental health problem. The proportion of males and females with a high GHQ12 score is unchanged from 2019/20. Considering the longer term trend, the proportion scoring highly is at a similar level to 2010/11. There was a significant worsening during the pandemic however the latest findings suggest an overall return to pre-pandemic levels. There are differences between subgroups of the population and a consistent gap remains between the most and least deprived areas. Further information on how to interpret the survey estimates and detail on the sample size and confidence intervals is available online: &lt;a href = 'https://view.officeapps.live.com/op/view.aspx?src=https%3A%2F%2Fwww.health-ni.gov.uk%2Fsites%2Fdefault%2Ffiles%2F2026-01%2Fghq12-pfg-tables-hsni.xlsx&amp;wdOrigin=BROWSELINK' target = '_blank'&gt;from this link. &lt;/a&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The comparison year has been set to 2021/22 due to changes in the data collection method as a result of Covid-19. The longer term trend also shows no change in life satisfaction since reporting began in 2014/15. However, consistent gaps remain between the most and least deprived areas, urban and rural areas, people with a disability compared to those without a disability, and also between people who are married or in a civil partnership compared with any other marital status. Of the 11 LGDs, Ards &amp; North Down have the highest rates of life satisfaction for 2024/25.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The comparison has been set to 2021/22 due to changes in the data collection method as a result of Covid-19. The longer term trend shows an improvement in self-efficacy since reporting began in 2014/15. Consistent gaps remain between males and females, the most and least deprived areas, and people with a disability compared with those without.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This suggests that international perceptions of Northern Ireland have remained broadly stable over that period.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Economic activity has increased gradually in recent years. Economic activity post-pandemic has recovered substantially and the latest 2024 data is now at a series high. Over the third quarter of 2025, economic output in Northern Ireland increased by 1.0%,  mainly driven by increased activity in the Services sector. Quarterly figures are available: &lt;a href = 'https://www.nisra.gov.uk/statistics/economic-output-statistics/ni-composite-economic-index' target = '_blank'&gt;from this link. &lt;/a&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">There has been a 14.5% decrease in real terms between 2020 and 2024. There has been a real terms decrease of 3.1% in GERD between 2023 and 2024. An improving trend is defined as anything more than a 0.1% increase on the 2020 GERD value; a worsening trend is defined as anything more than a 0.1% decrease on the 2020 GERD value.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Latest findings show the proportion, 6%, who felt very unsafe walking alone in their area after dark was the same as the 2021/22 figure, also 6%.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The figure for 2020/21 was the first year to reflect the impact of the Covid-19 pandemic on the workings of the justice system, which caused a backlog of cases to occur. While the impact of this backlog is still being reflected in the average time taken to complete cases, some improvement has been noted. The figure for 2024/25 (189 days) is lower than the figure for 2020/21 (193 days).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This means that fewer people aged 18+ see towns and city centres as safe and welcoming places for people of all walks of life than did in 2020.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Latest findings show the proportion, 5%, who felt very worried about becoming a victim of crime was similar to the 2021/22 figure, also 5%. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">The comparison year has been set to 2021/22 due to changes in the data collection method as a result of Covid-19. The longer term trend shows a spike in loneliness during the pandemic and appears to be returning to pre-pandemic levels since 2023/24. However, consistent gaps remain between the most and least deprived areas, people with a disability compared with those without, people who are married or in a civil partnership compared with those who are separated, divorced or widowed, and also between people with a white ethnicity compared with any other ethnicity.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">While the proportion of households who report being very satisfied or fairly satisified with their house or flat had improved in 2023/24, the level in 2024/25 is now similar to that in 2021/22.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This means that in 2024 a higher proportion of people aged 18+ think that relations between Protestants and Catholics are better now than they were five years ago as did in 2020.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This means that fewer people aged 18+ would prefer a mixed religion neighbourhood than did in 2020.</t>
   </si>
 </sst>
 </file>
@@ -585,8 +654,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:J53" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:J53"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:J105" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:J105"/>
   <tableColumns count="10">
     <tableColumn id="1" name="date"/>
     <tableColumn id="2" name="domain"/>
@@ -2570,6 +2639,1662 @@
         <v>170</v>
       </c>
     </row>
+    <row r="54">
+      <c r="A54" s="2" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B54" t="s">
+        <v>10</v>
+      </c>
+      <c r="C54" t="s">
+        <v>11</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>63</v>
+      </c>
+      <c r="F54" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H54" s="3" t="n">
+        <v>68</v>
+      </c>
+      <c r="I54" t="s">
+        <v>15</v>
+      </c>
+      <c r="J54" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B55" t="s">
+        <v>10</v>
+      </c>
+      <c r="C55" t="s">
+        <v>17</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E55" s="3" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="F55" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G55" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H55" s="3" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="I55" t="s">
+        <v>21</v>
+      </c>
+      <c r="J55" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B56" t="s">
+        <v>10</v>
+      </c>
+      <c r="C56" t="s">
+        <v>23</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="F56" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G56" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H56" s="3" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="I56" t="s">
+        <v>21</v>
+      </c>
+      <c r="J56" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B57" t="s">
+        <v>10</v>
+      </c>
+      <c r="C57" t="s">
+        <v>26</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E57" s="3" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H57" s="3" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="I57" t="s">
+        <v>30</v>
+      </c>
+      <c r="J57" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B58" t="s">
+        <v>32</v>
+      </c>
+      <c r="C58" t="s">
+        <v>33</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E58" s="3" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H58" s="3" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="I58" t="s">
+        <v>15</v>
+      </c>
+      <c r="J58" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B59" t="s">
+        <v>32</v>
+      </c>
+      <c r="C59" t="s">
+        <v>37</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E59" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H59" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="I59" t="s">
+        <v>30</v>
+      </c>
+      <c r="J59" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B60" t="s">
+        <v>32</v>
+      </c>
+      <c r="C60" t="s">
+        <v>39</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E60" s="3" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="F60" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H60" s="3" t="n">
+        <v>54.3</v>
+      </c>
+      <c r="I60" t="s">
+        <v>21</v>
+      </c>
+      <c r="J60" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B61" t="s">
+        <v>32</v>
+      </c>
+      <c r="C61" t="s">
+        <v>44</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="F61" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="G61" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H61" s="3" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="I61" t="s">
+        <v>15</v>
+      </c>
+      <c r="J61" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B62" t="s">
+        <v>32</v>
+      </c>
+      <c r="C62" t="s">
+        <v>47</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E62" s="3" t="n">
+        <v>47.9</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H62" s="3" t="n">
+        <v>47.8</v>
+      </c>
+      <c r="I62" t="s">
+        <v>30</v>
+      </c>
+      <c r="J62" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B63" t="s">
+        <v>32</v>
+      </c>
+      <c r="C63" t="s">
+        <v>50</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E63" s="3" t="n">
+        <v>51.9</v>
+      </c>
+      <c r="F63" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="G63" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H63" s="3" t="n">
+        <v>51</v>
+      </c>
+      <c r="I63" t="s">
+        <v>30</v>
+      </c>
+      <c r="J63" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B64" t="s">
+        <v>32</v>
+      </c>
+      <c r="C64" t="s">
+        <v>53</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E64" s="3" t="n">
+        <v>49.2</v>
+      </c>
+      <c r="F64" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="G64" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H64" s="3" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="I64" t="s">
+        <v>21</v>
+      </c>
+      <c r="J64" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B65" t="s">
+        <v>32</v>
+      </c>
+      <c r="C65" t="s">
+        <v>56</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E65" s="3" t="n">
+        <v>0.063</v>
+      </c>
+      <c r="F65" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="G65" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H65" s="3" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="I65" t="s">
+        <v>30</v>
+      </c>
+      <c r="J65" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B66" t="s">
+        <v>32</v>
+      </c>
+      <c r="C66" t="s">
+        <v>59</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E66" s="3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="F66" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H66" s="3" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="I66" t="s">
+        <v>30</v>
+      </c>
+      <c r="J66" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B67" t="s">
+        <v>63</v>
+      </c>
+      <c r="C67" t="s">
+        <v>64</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E67" s="3" t="n">
+        <v>49.6</v>
+      </c>
+      <c r="F67" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="G67" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H67" s="3" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="I67" t="s">
+        <v>15</v>
+      </c>
+      <c r="J67" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B68" t="s">
+        <v>63</v>
+      </c>
+      <c r="C68" t="s">
+        <v>67</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E68" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="F68" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="G68" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="H68" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="I68" t="s">
+        <v>30</v>
+      </c>
+      <c r="J68" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B69" t="s">
+        <v>63</v>
+      </c>
+      <c r="C69" t="s">
+        <v>71</v>
+      </c>
+      <c r="D69" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E69" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="F69" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="G69" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="H69" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="I69" t="s">
+        <v>30</v>
+      </c>
+      <c r="J69" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B70" t="s">
+        <v>63</v>
+      </c>
+      <c r="C70" t="s">
+        <v>73</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E70" s="3" t="n">
+        <v>36.1</v>
+      </c>
+      <c r="F70" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="G70" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H70" s="3" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="I70" t="s">
+        <v>21</v>
+      </c>
+      <c r="J70" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B71" t="s">
+        <v>75</v>
+      </c>
+      <c r="C71" t="s">
+        <v>76</v>
+      </c>
+      <c r="D71" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E71" s="3" t="n">
+        <v>56</v>
+      </c>
+      <c r="F71" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="G71" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H71" s="3" t="n">
+        <v>56.3</v>
+      </c>
+      <c r="I71" t="s">
+        <v>30</v>
+      </c>
+      <c r="J71" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B72" t="s">
+        <v>75</v>
+      </c>
+      <c r="C72" t="s">
+        <v>78</v>
+      </c>
+      <c r="D72" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="E72" s="3" t="n">
+        <v>62.1</v>
+      </c>
+      <c r="F72" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="H72" s="3" t="n">
+        <v>60.2</v>
+      </c>
+      <c r="I72" t="s">
+        <v>21</v>
+      </c>
+      <c r="J72" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B73" t="s">
+        <v>75</v>
+      </c>
+      <c r="C73" t="s">
+        <v>83</v>
+      </c>
+      <c r="D73" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="E73" s="3" t="n">
+        <v>60.1</v>
+      </c>
+      <c r="F73" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="G73" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="H73" s="3" t="n">
+        <v>59.3</v>
+      </c>
+      <c r="I73" t="s">
+        <v>30</v>
+      </c>
+      <c r="J73" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B74" t="s">
+        <v>75</v>
+      </c>
+      <c r="C74" t="s">
+        <v>86</v>
+      </c>
+      <c r="D74" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E74" s="3" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="F74" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="G74" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="H74" s="3" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="I74" t="s">
+        <v>30</v>
+      </c>
+      <c r="J74" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B75" t="s">
+        <v>75</v>
+      </c>
+      <c r="C75" t="s">
+        <v>89</v>
+      </c>
+      <c r="D75" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="E75" s="3" t="n">
+        <v>169</v>
+      </c>
+      <c r="F75" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="G75" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H75" s="3" t="n">
+        <v>177</v>
+      </c>
+      <c r="I75" t="s">
+        <v>21</v>
+      </c>
+      <c r="J75" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B76" t="s">
+        <v>75</v>
+      </c>
+      <c r="C76" t="s">
+        <v>94</v>
+      </c>
+      <c r="D76" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E76" s="3" t="n">
+        <v>75</v>
+      </c>
+      <c r="F76" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="G76" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="H76" s="3" t="n">
+        <v>74</v>
+      </c>
+      <c r="I76" t="s">
+        <v>30</v>
+      </c>
+      <c r="J76" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B77" t="s">
+        <v>98</v>
+      </c>
+      <c r="C77" t="s">
+        <v>99</v>
+      </c>
+      <c r="D77" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E77" s="3" t="n">
+        <v>62</v>
+      </c>
+      <c r="F77" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="G77" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="H77" s="3" t="n">
+        <v>83</v>
+      </c>
+      <c r="I77" t="s">
+        <v>15</v>
+      </c>
+      <c r="J77" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B78" t="s">
+        <v>98</v>
+      </c>
+      <c r="C78" t="s">
+        <v>101</v>
+      </c>
+      <c r="D78" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E78" s="3" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="F78" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="G78" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H78" s="3" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="I78" t="s">
+        <v>30</v>
+      </c>
+      <c r="J78" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B79" t="s">
+        <v>98</v>
+      </c>
+      <c r="C79" t="s">
+        <v>104</v>
+      </c>
+      <c r="D79" s="3"/>
+      <c r="E79" s="3"/>
+      <c r="F79" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="G79" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="H79" s="3" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="I79" t="s">
+        <v>61</v>
+      </c>
+      <c r="J79" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B80" t="s">
+        <v>98</v>
+      </c>
+      <c r="C80" t="s">
+        <v>106</v>
+      </c>
+      <c r="D80" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E80" s="3" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="F80" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="G80" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H80" s="3" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="I80" t="s">
+        <v>21</v>
+      </c>
+      <c r="J80" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B81" t="s">
+        <v>108</v>
+      </c>
+      <c r="C81" t="s">
+        <v>109</v>
+      </c>
+      <c r="D81" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E81" s="3" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="F81" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="G81" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H81" s="3" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="I81" t="s">
+        <v>15</v>
+      </c>
+      <c r="J81" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B82" t="s">
+        <v>108</v>
+      </c>
+      <c r="C82" t="s">
+        <v>111</v>
+      </c>
+      <c r="D82" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E82" s="3" t="n">
+        <v>69.8</v>
+      </c>
+      <c r="F82" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="G82" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H82" s="3" t="n">
+        <v>74.3</v>
+      </c>
+      <c r="I82" t="s">
+        <v>15</v>
+      </c>
+      <c r="J82" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B83" t="s">
+        <v>108</v>
+      </c>
+      <c r="C83" t="s">
+        <v>114</v>
+      </c>
+      <c r="D83" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E83" s="3" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H83" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="I83" t="s">
+        <v>30</v>
+      </c>
+      <c r="J83" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B84" t="s">
+        <v>108</v>
+      </c>
+      <c r="C84" t="s">
+        <v>117</v>
+      </c>
+      <c r="D84" s="3"/>
+      <c r="E84" s="3"/>
+      <c r="F84" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G84" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H84" s="3" t="n">
+        <v>69</v>
+      </c>
+      <c r="I84" t="s">
+        <v>61</v>
+      </c>
+      <c r="J84" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B85" t="s">
+        <v>108</v>
+      </c>
+      <c r="C85" t="s">
+        <v>119</v>
+      </c>
+      <c r="D85" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="E85" s="3" t="n">
+        <v>61.27</v>
+      </c>
+      <c r="F85" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G85" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H85" s="3" t="n">
+        <v>62.21</v>
+      </c>
+      <c r="I85" t="s">
+        <v>30</v>
+      </c>
+      <c r="J85" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B86" t="s">
+        <v>108</v>
+      </c>
+      <c r="C86" t="s">
+        <v>121</v>
+      </c>
+      <c r="D86" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E86" s="3" t="n">
+        <v>92.8</v>
+      </c>
+      <c r="F86" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G86" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H86" s="3" t="n">
+        <v>99.5</v>
+      </c>
+      <c r="I86" t="s">
+        <v>15</v>
+      </c>
+      <c r="J86" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B87" t="s">
+        <v>108</v>
+      </c>
+      <c r="C87" t="s">
+        <v>123</v>
+      </c>
+      <c r="D87" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="E87" s="3" t="n">
+        <v>96.3</v>
+      </c>
+      <c r="F87" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G87" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H87" s="3" t="n">
+        <v>102.4</v>
+      </c>
+      <c r="I87" t="s">
+        <v>15</v>
+      </c>
+      <c r="J87" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B88" t="s">
+        <v>108</v>
+      </c>
+      <c r="C88" t="s">
+        <v>126</v>
+      </c>
+      <c r="D88" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E88" s="3" t="n">
+        <v>1170.4</v>
+      </c>
+      <c r="F88" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G88" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H88" s="3" t="n">
+        <v>1000.7</v>
+      </c>
+      <c r="I88" t="s">
+        <v>21</v>
+      </c>
+      <c r="J88" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B89" t="s">
+        <v>108</v>
+      </c>
+      <c r="C89" t="s">
+        <v>128</v>
+      </c>
+      <c r="D89" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E89" s="3" t="n">
+        <v>76.3</v>
+      </c>
+      <c r="F89" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="G89" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H89" s="3" t="n">
+        <v>80.4</v>
+      </c>
+      <c r="I89" t="s">
+        <v>15</v>
+      </c>
+      <c r="J89" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B90" t="s">
+        <v>131</v>
+      </c>
+      <c r="C90" t="s">
+        <v>132</v>
+      </c>
+      <c r="D90" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E90" s="3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="F90" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="G90" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="H90" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I90" t="s">
+        <v>30</v>
+      </c>
+      <c r="J90" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B91" t="s">
+        <v>131</v>
+      </c>
+      <c r="C91" t="s">
+        <v>134</v>
+      </c>
+      <c r="D91" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E91" s="3" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="H91" s="3" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="I91" t="s">
+        <v>30</v>
+      </c>
+      <c r="J91" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B92" t="s">
+        <v>131</v>
+      </c>
+      <c r="C92" t="s">
+        <v>136</v>
+      </c>
+      <c r="D92" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="E92" s="3" t="n">
+        <v>193</v>
+      </c>
+      <c r="F92" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="G92" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H92" s="3" t="n">
+        <v>189</v>
+      </c>
+      <c r="I92" t="s">
+        <v>30</v>
+      </c>
+      <c r="J92" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B93" t="s">
+        <v>131</v>
+      </c>
+      <c r="C93" t="s">
+        <v>140</v>
+      </c>
+      <c r="D93" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E93" s="3" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="F93" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="G93" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H93" s="3" t="n">
+        <v>40.7</v>
+      </c>
+      <c r="I93" t="s">
+        <v>21</v>
+      </c>
+      <c r="J93" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B94" t="s">
+        <v>131</v>
+      </c>
+      <c r="C94" t="s">
+        <v>142</v>
+      </c>
+      <c r="D94" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E94" s="3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="H94" s="3" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="I94" t="s">
+        <v>30</v>
+      </c>
+      <c r="J94" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B95" t="s">
+        <v>145</v>
+      </c>
+      <c r="C95" t="s">
+        <v>146</v>
+      </c>
+      <c r="D95" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E95" s="3" t="n">
+        <v>68.4</v>
+      </c>
+      <c r="F95" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G95" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H95" s="3" t="n">
+        <v>69.2</v>
+      </c>
+      <c r="I95" t="s">
+        <v>30</v>
+      </c>
+      <c r="J95" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B96" t="s">
+        <v>145</v>
+      </c>
+      <c r="C96" t="s">
+        <v>148</v>
+      </c>
+      <c r="D96" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E96" s="3" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H96" s="3" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="I96" t="s">
+        <v>15</v>
+      </c>
+      <c r="J96" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B97" t="s">
+        <v>145</v>
+      </c>
+      <c r="C97" t="s">
+        <v>150</v>
+      </c>
+      <c r="D97" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="E97" s="3" t="n">
+        <v>47</v>
+      </c>
+      <c r="F97" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="G97" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H97" s="3" t="n">
+        <v>46</v>
+      </c>
+      <c r="I97" t="s">
+        <v>30</v>
+      </c>
+      <c r="J97" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B98" t="s">
+        <v>152</v>
+      </c>
+      <c r="C98" t="s">
+        <v>153</v>
+      </c>
+      <c r="D98" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E98" s="3" t="n">
+        <v>90</v>
+      </c>
+      <c r="F98" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="G98" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H98" s="3" t="n">
+        <v>91</v>
+      </c>
+      <c r="I98" t="s">
+        <v>30</v>
+      </c>
+      <c r="J98" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B99" t="s">
+        <v>152</v>
+      </c>
+      <c r="C99" t="s">
+        <v>154</v>
+      </c>
+      <c r="D99" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E99" s="3" t="n">
+        <v>10135</v>
+      </c>
+      <c r="F99" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="G99" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H99" s="3" t="n">
+        <v>10855</v>
+      </c>
+      <c r="I99" t="s">
+        <v>21</v>
+      </c>
+      <c r="J99" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B100" t="s">
+        <v>152</v>
+      </c>
+      <c r="C100" t="s">
+        <v>156</v>
+      </c>
+      <c r="D100" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E100" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="H100" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="I100" t="s">
+        <v>30</v>
+      </c>
+      <c r="J100" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B101" t="s">
+        <v>152</v>
+      </c>
+      <c r="C101" t="s">
+        <v>159</v>
+      </c>
+      <c r="D101" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="E101" s="3" t="n">
+        <v>30288</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H101" s="3" t="n">
+        <v>37635</v>
+      </c>
+      <c r="I101" t="s">
+        <v>21</v>
+      </c>
+      <c r="J101" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B102" t="s">
+        <v>161</v>
+      </c>
+      <c r="C102" t="s">
+        <v>162</v>
+      </c>
+      <c r="D102" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E102" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="F102" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="G102" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H102" s="3" t="n">
+        <v>46.7</v>
+      </c>
+      <c r="I102" t="s">
+        <v>15</v>
+      </c>
+      <c r="J102" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B103" t="s">
+        <v>161</v>
+      </c>
+      <c r="C103" t="s">
+        <v>164</v>
+      </c>
+      <c r="D103" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E103" s="3" t="n">
+        <v>78.6</v>
+      </c>
+      <c r="F103" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="G103" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H103" s="3" t="n">
+        <v>76.1</v>
+      </c>
+      <c r="I103" t="s">
+        <v>21</v>
+      </c>
+      <c r="J103" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B104" t="s">
+        <v>161</v>
+      </c>
+      <c r="C104" t="s">
+        <v>165</v>
+      </c>
+      <c r="D104" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E104" s="3" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="F104" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="G104" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H104" s="3" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="I104" t="s">
+        <v>30</v>
+      </c>
+      <c r="J104" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B105" t="s">
+        <v>161</v>
+      </c>
+      <c r="C105" t="s">
+        <v>168</v>
+      </c>
+      <c r="D105" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E105" s="3" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="F105" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="G105" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H105" s="3" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="I105" t="s">
+        <v>30</v>
+      </c>
+      <c r="J105" t="s">
+        <v>170</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/indicator-performance-table.xlsx
+++ b/indicator-performance-table.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="195">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -594,6 +594,9 @@
   </si>
   <si>
     <t xml:space="preserve">This means that fewer people aged 18+ would prefer a mixed religion neighbourhood than did in 2020.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2020-24</t>
   </si>
 </sst>
 </file>
@@ -654,8 +657,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:J105" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:J105"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:J157" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:J157"/>
   <tableColumns count="10">
     <tableColumn id="1" name="date"/>
     <tableColumn id="2" name="domain"/>
@@ -4295,6 +4298,1662 @@
         <v>170</v>
       </c>
     </row>
+    <row r="106">
+      <c r="A106" s="2" t="n">
+        <v>46176</v>
+      </c>
+      <c r="B106" t="s">
+        <v>10</v>
+      </c>
+      <c r="C106" t="s">
+        <v>11</v>
+      </c>
+      <c r="D106" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E106" s="3" t="n">
+        <v>63</v>
+      </c>
+      <c r="F106" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G106" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H106" s="3" t="n">
+        <v>68</v>
+      </c>
+      <c r="I106" t="s">
+        <v>15</v>
+      </c>
+      <c r="J106" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="n">
+        <v>46176</v>
+      </c>
+      <c r="B107" t="s">
+        <v>10</v>
+      </c>
+      <c r="C107" t="s">
+        <v>17</v>
+      </c>
+      <c r="D107" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E107" s="3" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="F107" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G107" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H107" s="3" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="I107" t="s">
+        <v>21</v>
+      </c>
+      <c r="J107" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="n">
+        <v>46176</v>
+      </c>
+      <c r="B108" t="s">
+        <v>10</v>
+      </c>
+      <c r="C108" t="s">
+        <v>23</v>
+      </c>
+      <c r="D108" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E108" s="3" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="F108" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G108" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H108" s="3" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="I108" t="s">
+        <v>21</v>
+      </c>
+      <c r="J108" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="n">
+        <v>46176</v>
+      </c>
+      <c r="B109" t="s">
+        <v>10</v>
+      </c>
+      <c r="C109" t="s">
+        <v>26</v>
+      </c>
+      <c r="D109" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E109" s="3" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="F109" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G109" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H109" s="3" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="I109" t="s">
+        <v>30</v>
+      </c>
+      <c r="J109" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="n">
+        <v>46176</v>
+      </c>
+      <c r="B110" t="s">
+        <v>32</v>
+      </c>
+      <c r="C110" t="s">
+        <v>33</v>
+      </c>
+      <c r="D110" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E110" s="3" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="F110" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G110" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H110" s="3" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="I110" t="s">
+        <v>15</v>
+      </c>
+      <c r="J110" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="n">
+        <v>46176</v>
+      </c>
+      <c r="B111" t="s">
+        <v>32</v>
+      </c>
+      <c r="C111" t="s">
+        <v>37</v>
+      </c>
+      <c r="D111" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E111" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="F111" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G111" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H111" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="I111" t="s">
+        <v>30</v>
+      </c>
+      <c r="J111" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="n">
+        <v>46176</v>
+      </c>
+      <c r="B112" t="s">
+        <v>32</v>
+      </c>
+      <c r="C112" t="s">
+        <v>39</v>
+      </c>
+      <c r="D112" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E112" s="3" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="F112" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="G112" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H112" s="3" t="n">
+        <v>54.3</v>
+      </c>
+      <c r="I112" t="s">
+        <v>21</v>
+      </c>
+      <c r="J112" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="n">
+        <v>46176</v>
+      </c>
+      <c r="B113" t="s">
+        <v>32</v>
+      </c>
+      <c r="C113" t="s">
+        <v>44</v>
+      </c>
+      <c r="D113" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E113" s="3" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="F113" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="G113" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H113" s="3" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="I113" t="s">
+        <v>15</v>
+      </c>
+      <c r="J113" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="n">
+        <v>46176</v>
+      </c>
+      <c r="B114" t="s">
+        <v>32</v>
+      </c>
+      <c r="C114" t="s">
+        <v>47</v>
+      </c>
+      <c r="D114" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E114" s="3" t="n">
+        <v>47.9</v>
+      </c>
+      <c r="F114" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G114" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H114" s="3" t="n">
+        <v>47.8</v>
+      </c>
+      <c r="I114" t="s">
+        <v>30</v>
+      </c>
+      <c r="J114" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="n">
+        <v>46176</v>
+      </c>
+      <c r="B115" t="s">
+        <v>32</v>
+      </c>
+      <c r="C115" t="s">
+        <v>50</v>
+      </c>
+      <c r="D115" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E115" s="3" t="n">
+        <v>51.9</v>
+      </c>
+      <c r="F115" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="G115" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H115" s="3" t="n">
+        <v>51</v>
+      </c>
+      <c r="I115" t="s">
+        <v>30</v>
+      </c>
+      <c r="J115" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="n">
+        <v>46176</v>
+      </c>
+      <c r="B116" t="s">
+        <v>32</v>
+      </c>
+      <c r="C116" t="s">
+        <v>53</v>
+      </c>
+      <c r="D116" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E116" s="3" t="n">
+        <v>49.2</v>
+      </c>
+      <c r="F116" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="G116" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H116" s="3" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="I116" t="s">
+        <v>21</v>
+      </c>
+      <c r="J116" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46176</v>
+      </c>
+      <c r="B117" t="s">
+        <v>32</v>
+      </c>
+      <c r="C117" t="s">
+        <v>56</v>
+      </c>
+      <c r="D117" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E117" s="3" t="n">
+        <v>0.063</v>
+      </c>
+      <c r="F117" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="G117" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H117" s="3" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="I117" t="s">
+        <v>30</v>
+      </c>
+      <c r="J117" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46176</v>
+      </c>
+      <c r="B118" t="s">
+        <v>32</v>
+      </c>
+      <c r="C118" t="s">
+        <v>59</v>
+      </c>
+      <c r="D118" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E118" s="3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="F118" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="G118" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H118" s="3" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="I118" t="s">
+        <v>30</v>
+      </c>
+      <c r="J118" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46176</v>
+      </c>
+      <c r="B119" t="s">
+        <v>63</v>
+      </c>
+      <c r="C119" t="s">
+        <v>64</v>
+      </c>
+      <c r="D119" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E119" s="3" t="n">
+        <v>49.6</v>
+      </c>
+      <c r="F119" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="G119" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H119" s="3" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="I119" t="s">
+        <v>15</v>
+      </c>
+      <c r="J119" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46176</v>
+      </c>
+      <c r="B120" t="s">
+        <v>63</v>
+      </c>
+      <c r="C120" t="s">
+        <v>67</v>
+      </c>
+      <c r="D120" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E120" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="F120" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="G120" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="H120" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="I120" t="s">
+        <v>30</v>
+      </c>
+      <c r="J120" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46176</v>
+      </c>
+      <c r="B121" t="s">
+        <v>63</v>
+      </c>
+      <c r="C121" t="s">
+        <v>71</v>
+      </c>
+      <c r="D121" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E121" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="F121" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="G121" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="H121" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="I121" t="s">
+        <v>30</v>
+      </c>
+      <c r="J121" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46176</v>
+      </c>
+      <c r="B122" t="s">
+        <v>63</v>
+      </c>
+      <c r="C122" t="s">
+        <v>73</v>
+      </c>
+      <c r="D122" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E122" s="3" t="n">
+        <v>36.1</v>
+      </c>
+      <c r="F122" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="G122" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H122" s="3" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="I122" t="s">
+        <v>21</v>
+      </c>
+      <c r="J122" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46176</v>
+      </c>
+      <c r="B123" t="s">
+        <v>75</v>
+      </c>
+      <c r="C123" t="s">
+        <v>76</v>
+      </c>
+      <c r="D123" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E123" s="3" t="n">
+        <v>56</v>
+      </c>
+      <c r="F123" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="G123" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H123" s="3" t="n">
+        <v>56.3</v>
+      </c>
+      <c r="I123" t="s">
+        <v>30</v>
+      </c>
+      <c r="J123" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46176</v>
+      </c>
+      <c r="B124" t="s">
+        <v>75</v>
+      </c>
+      <c r="C124" t="s">
+        <v>78</v>
+      </c>
+      <c r="D124" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="E124" s="3" t="n">
+        <v>62.1</v>
+      </c>
+      <c r="F124" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="G124" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="H124" s="3" t="n">
+        <v>60.2</v>
+      </c>
+      <c r="I124" t="s">
+        <v>21</v>
+      </c>
+      <c r="J124" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46176</v>
+      </c>
+      <c r="B125" t="s">
+        <v>75</v>
+      </c>
+      <c r="C125" t="s">
+        <v>83</v>
+      </c>
+      <c r="D125" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="E125" s="3" t="n">
+        <v>60.1</v>
+      </c>
+      <c r="F125" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="G125" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="H125" s="3" t="n">
+        <v>59.3</v>
+      </c>
+      <c r="I125" t="s">
+        <v>30</v>
+      </c>
+      <c r="J125" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46176</v>
+      </c>
+      <c r="B126" t="s">
+        <v>75</v>
+      </c>
+      <c r="C126" t="s">
+        <v>86</v>
+      </c>
+      <c r="D126" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E126" s="3" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="F126" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="G126" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H126" s="3" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="I126" t="s">
+        <v>15</v>
+      </c>
+      <c r="J126" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46176</v>
+      </c>
+      <c r="B127" t="s">
+        <v>75</v>
+      </c>
+      <c r="C127" t="s">
+        <v>89</v>
+      </c>
+      <c r="D127" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="E127" s="3" t="n">
+        <v>169</v>
+      </c>
+      <c r="F127" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="G127" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="H127" s="3" t="n">
+        <v>181</v>
+      </c>
+      <c r="I127" t="s">
+        <v>21</v>
+      </c>
+      <c r="J127" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46176</v>
+      </c>
+      <c r="B128" t="s">
+        <v>75</v>
+      </c>
+      <c r="C128" t="s">
+        <v>94</v>
+      </c>
+      <c r="D128" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E128" s="3" t="n">
+        <v>75</v>
+      </c>
+      <c r="F128" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="G128" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H128" s="3" t="n">
+        <v>73</v>
+      </c>
+      <c r="I128" t="s">
+        <v>30</v>
+      </c>
+      <c r="J128" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46176</v>
+      </c>
+      <c r="B129" t="s">
+        <v>98</v>
+      </c>
+      <c r="C129" t="s">
+        <v>99</v>
+      </c>
+      <c r="D129" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E129" s="3" t="n">
+        <v>62</v>
+      </c>
+      <c r="F129" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="G129" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H129" s="3" t="n">
+        <v>85</v>
+      </c>
+      <c r="I129" t="s">
+        <v>15</v>
+      </c>
+      <c r="J129" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46176</v>
+      </c>
+      <c r="B130" t="s">
+        <v>98</v>
+      </c>
+      <c r="C130" t="s">
+        <v>101</v>
+      </c>
+      <c r="D130" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E130" s="3" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="F130" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="G130" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H130" s="3" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="I130" t="s">
+        <v>30</v>
+      </c>
+      <c r="J130" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46176</v>
+      </c>
+      <c r="B131" t="s">
+        <v>98</v>
+      </c>
+      <c r="C131" t="s">
+        <v>104</v>
+      </c>
+      <c r="D131" s="3"/>
+      <c r="E131" s="3"/>
+      <c r="F131" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="G131" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="H131" s="3" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="I131" t="s">
+        <v>61</v>
+      </c>
+      <c r="J131" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46176</v>
+      </c>
+      <c r="B132" t="s">
+        <v>98</v>
+      </c>
+      <c r="C132" t="s">
+        <v>106</v>
+      </c>
+      <c r="D132" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E132" s="3" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="F132" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="G132" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H132" s="3" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="I132" t="s">
+        <v>21</v>
+      </c>
+      <c r="J132" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46176</v>
+      </c>
+      <c r="B133" t="s">
+        <v>108</v>
+      </c>
+      <c r="C133" t="s">
+        <v>109</v>
+      </c>
+      <c r="D133" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E133" s="3" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="F133" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="G133" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H133" s="3" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="I133" t="s">
+        <v>15</v>
+      </c>
+      <c r="J133" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46176</v>
+      </c>
+      <c r="B134" t="s">
+        <v>108</v>
+      </c>
+      <c r="C134" t="s">
+        <v>111</v>
+      </c>
+      <c r="D134" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E134" s="3" t="n">
+        <v>69.8</v>
+      </c>
+      <c r="F134" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="G134" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H134" s="3" t="n">
+        <v>74.3</v>
+      </c>
+      <c r="I134" t="s">
+        <v>15</v>
+      </c>
+      <c r="J134" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46176</v>
+      </c>
+      <c r="B135" t="s">
+        <v>108</v>
+      </c>
+      <c r="C135" t="s">
+        <v>114</v>
+      </c>
+      <c r="D135" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E135" s="3" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="F135" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="G135" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H135" s="3" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="I135" t="s">
+        <v>15</v>
+      </c>
+      <c r="J135" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46176</v>
+      </c>
+      <c r="B136" t="s">
+        <v>108</v>
+      </c>
+      <c r="C136" t="s">
+        <v>117</v>
+      </c>
+      <c r="D136" s="3"/>
+      <c r="E136" s="3"/>
+      <c r="F136" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G136" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H136" s="3" t="n">
+        <v>69</v>
+      </c>
+      <c r="I136" t="s">
+        <v>61</v>
+      </c>
+      <c r="J136" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46176</v>
+      </c>
+      <c r="B137" t="s">
+        <v>108</v>
+      </c>
+      <c r="C137" t="s">
+        <v>119</v>
+      </c>
+      <c r="D137" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="E137" s="3" t="n">
+        <v>61.27</v>
+      </c>
+      <c r="F137" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G137" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H137" s="3" t="n">
+        <v>62.21</v>
+      </c>
+      <c r="I137" t="s">
+        <v>30</v>
+      </c>
+      <c r="J137" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46176</v>
+      </c>
+      <c r="B138" t="s">
+        <v>108</v>
+      </c>
+      <c r="C138" t="s">
+        <v>121</v>
+      </c>
+      <c r="D138" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E138" s="3" t="n">
+        <v>92.8</v>
+      </c>
+      <c r="F138" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G138" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H138" s="3" t="n">
+        <v>99.5</v>
+      </c>
+      <c r="I138" t="s">
+        <v>15</v>
+      </c>
+      <c r="J138" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46176</v>
+      </c>
+      <c r="B139" t="s">
+        <v>108</v>
+      </c>
+      <c r="C139" t="s">
+        <v>123</v>
+      </c>
+      <c r="D139" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="E139" s="3" t="n">
+        <v>96.3</v>
+      </c>
+      <c r="F139" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G139" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H139" s="3" t="n">
+        <v>104.4</v>
+      </c>
+      <c r="I139" t="s">
+        <v>15</v>
+      </c>
+      <c r="J139" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46176</v>
+      </c>
+      <c r="B140" t="s">
+        <v>108</v>
+      </c>
+      <c r="C140" t="s">
+        <v>126</v>
+      </c>
+      <c r="D140" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E140" s="3" t="n">
+        <v>1170.4</v>
+      </c>
+      <c r="F140" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G140" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H140" s="3" t="n">
+        <v>1000.7</v>
+      </c>
+      <c r="I140" t="s">
+        <v>21</v>
+      </c>
+      <c r="J140" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46176</v>
+      </c>
+      <c r="B141" t="s">
+        <v>108</v>
+      </c>
+      <c r="C141" t="s">
+        <v>128</v>
+      </c>
+      <c r="D141" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E141" s="3" t="n">
+        <v>76.3</v>
+      </c>
+      <c r="F141" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="G141" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H141" s="3" t="n">
+        <v>80.4</v>
+      </c>
+      <c r="I141" t="s">
+        <v>15</v>
+      </c>
+      <c r="J141" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46176</v>
+      </c>
+      <c r="B142" t="s">
+        <v>131</v>
+      </c>
+      <c r="C142" t="s">
+        <v>132</v>
+      </c>
+      <c r="D142" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E142" s="3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="F142" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="G142" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="H142" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I142" t="s">
+        <v>30</v>
+      </c>
+      <c r="J142" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46176</v>
+      </c>
+      <c r="B143" t="s">
+        <v>131</v>
+      </c>
+      <c r="C143" t="s">
+        <v>134</v>
+      </c>
+      <c r="D143" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E143" s="3" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="F143" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="G143" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="H143" s="3" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="I143" t="s">
+        <v>30</v>
+      </c>
+      <c r="J143" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="n">
+        <v>46176</v>
+      </c>
+      <c r="B144" t="s">
+        <v>131</v>
+      </c>
+      <c r="C144" t="s">
+        <v>136</v>
+      </c>
+      <c r="D144" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="E144" s="3" t="n">
+        <v>193</v>
+      </c>
+      <c r="F144" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="G144" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H144" s="3" t="n">
+        <v>189</v>
+      </c>
+      <c r="I144" t="s">
+        <v>30</v>
+      </c>
+      <c r="J144" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="n">
+        <v>46176</v>
+      </c>
+      <c r="B145" t="s">
+        <v>131</v>
+      </c>
+      <c r="C145" t="s">
+        <v>140</v>
+      </c>
+      <c r="D145" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E145" s="3" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="F145" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="G145" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H145" s="3" t="n">
+        <v>40.7</v>
+      </c>
+      <c r="I145" t="s">
+        <v>21</v>
+      </c>
+      <c r="J145" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="n">
+        <v>46176</v>
+      </c>
+      <c r="B146" t="s">
+        <v>131</v>
+      </c>
+      <c r="C146" t="s">
+        <v>142</v>
+      </c>
+      <c r="D146" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E146" s="3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="F146" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="G146" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="H146" s="3" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="I146" t="s">
+        <v>30</v>
+      </c>
+      <c r="J146" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="n">
+        <v>46176</v>
+      </c>
+      <c r="B147" t="s">
+        <v>145</v>
+      </c>
+      <c r="C147" t="s">
+        <v>146</v>
+      </c>
+      <c r="D147" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E147" s="3" t="n">
+        <v>68.4</v>
+      </c>
+      <c r="F147" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G147" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H147" s="3" t="n">
+        <v>69.2</v>
+      </c>
+      <c r="I147" t="s">
+        <v>30</v>
+      </c>
+      <c r="J147" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="n">
+        <v>46176</v>
+      </c>
+      <c r="B148" t="s">
+        <v>145</v>
+      </c>
+      <c r="C148" t="s">
+        <v>148</v>
+      </c>
+      <c r="D148" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E148" s="3" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="F148" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="G148" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H148" s="3" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="I148" t="s">
+        <v>15</v>
+      </c>
+      <c r="J148" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="n">
+        <v>46176</v>
+      </c>
+      <c r="B149" t="s">
+        <v>145</v>
+      </c>
+      <c r="C149" t="s">
+        <v>150</v>
+      </c>
+      <c r="D149" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="E149" s="3" t="n">
+        <v>47</v>
+      </c>
+      <c r="F149" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="G149" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H149" s="3" t="n">
+        <v>46</v>
+      </c>
+      <c r="I149" t="s">
+        <v>30</v>
+      </c>
+      <c r="J149" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="n">
+        <v>46176</v>
+      </c>
+      <c r="B150" t="s">
+        <v>152</v>
+      </c>
+      <c r="C150" t="s">
+        <v>153</v>
+      </c>
+      <c r="D150" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E150" s="3" t="n">
+        <v>90</v>
+      </c>
+      <c r="F150" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="G150" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H150" s="3" t="n">
+        <v>91</v>
+      </c>
+      <c r="I150" t="s">
+        <v>30</v>
+      </c>
+      <c r="J150" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="n">
+        <v>46176</v>
+      </c>
+      <c r="B151" t="s">
+        <v>152</v>
+      </c>
+      <c r="C151" t="s">
+        <v>154</v>
+      </c>
+      <c r="D151" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E151" s="3" t="n">
+        <v>10135</v>
+      </c>
+      <c r="F151" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="G151" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H151" s="3" t="n">
+        <v>10855</v>
+      </c>
+      <c r="I151" t="s">
+        <v>21</v>
+      </c>
+      <c r="J151" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="n">
+        <v>46176</v>
+      </c>
+      <c r="B152" t="s">
+        <v>152</v>
+      </c>
+      <c r="C152" t="s">
+        <v>156</v>
+      </c>
+      <c r="D152" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E152" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F152" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="G152" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="H152" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="I152" t="s">
+        <v>30</v>
+      </c>
+      <c r="J152" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="n">
+        <v>46176</v>
+      </c>
+      <c r="B153" t="s">
+        <v>152</v>
+      </c>
+      <c r="C153" t="s">
+        <v>159</v>
+      </c>
+      <c r="D153" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="E153" s="3" t="n">
+        <v>30288</v>
+      </c>
+      <c r="F153" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="G153" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H153" s="3" t="n">
+        <v>37635</v>
+      </c>
+      <c r="I153" t="s">
+        <v>21</v>
+      </c>
+      <c r="J153" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="n">
+        <v>46176</v>
+      </c>
+      <c r="B154" t="s">
+        <v>161</v>
+      </c>
+      <c r="C154" t="s">
+        <v>162</v>
+      </c>
+      <c r="D154" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E154" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="F154" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="G154" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H154" s="3" t="n">
+        <v>46.7</v>
+      </c>
+      <c r="I154" t="s">
+        <v>15</v>
+      </c>
+      <c r="J154" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="n">
+        <v>46176</v>
+      </c>
+      <c r="B155" t="s">
+        <v>161</v>
+      </c>
+      <c r="C155" t="s">
+        <v>164</v>
+      </c>
+      <c r="D155" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E155" s="3" t="n">
+        <v>78.6</v>
+      </c>
+      <c r="F155" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="G155" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H155" s="3" t="n">
+        <v>76.1</v>
+      </c>
+      <c r="I155" t="s">
+        <v>21</v>
+      </c>
+      <c r="J155" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="n">
+        <v>46176</v>
+      </c>
+      <c r="B156" t="s">
+        <v>161</v>
+      </c>
+      <c r="C156" t="s">
+        <v>165</v>
+      </c>
+      <c r="D156" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E156" s="3" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="F156" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="G156" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H156" s="3" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="I156" t="s">
+        <v>30</v>
+      </c>
+      <c r="J156" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="n">
+        <v>46176</v>
+      </c>
+      <c r="B157" t="s">
+        <v>161</v>
+      </c>
+      <c r="C157" t="s">
+        <v>168</v>
+      </c>
+      <c r="D157" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E157" s="3" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="F157" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="G157" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H157" s="3" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="I157" t="s">
+        <v>30</v>
+      </c>
+      <c r="J157" t="s">
+        <v>170</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/indicator-performance-table.xlsx
+++ b/indicator-performance-table.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="196">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -594,6 +594,9 @@
   </si>
   <si>
     <t xml:space="preserve">This means that fewer people aged 18+ would prefer a mixed religion neighbourhood than did in 2020.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The indicator shows that the percentage of households with accessible natural space within 400 metres has decreased since the comparision year 2023. 47.8 per cent of households are within 400m of greenspace &gt;2ha, and off-road trails in 2025.</t>
   </si>
   <si>
     <t xml:space="preserve">2020-24</t>
@@ -4580,10 +4583,10 @@
         <v>47.8</v>
       </c>
       <c r="I114" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="J114" t="s">
-        <v>49</v>
+        <v>194</v>
       </c>
     </row>
     <row r="115">
@@ -4990,7 +4993,7 @@
         <v>91</v>
       </c>
       <c r="G127" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H127" s="3" t="n">
         <v>181</v>
@@ -5028,10 +5031,10 @@
         <v>73</v>
       </c>
       <c r="I128" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="J128" t="s">
-        <v>97</v>
+        <v>49</v>
       </c>
     </row>
     <row r="129">

--- a/indicator-performance-table.xlsx
+++ b/indicator-performance-table.xlsx
@@ -606,8 +606,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
-    <numFmt numFmtId="165" formatCode="mm/dd/yyyy"/>
+  <numFmts count="1">
     <numFmt numFmtId="166" formatCode="dd/mm/yyyy"/>
   </numFmts>
   <fonts count="2">
@@ -646,7 +645,7 @@
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>

--- a/indicator-performance-table.xlsx
+++ b/indicator-performance-table.xlsx
@@ -659,8 +659,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:J157" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:J157"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:J209" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:J209"/>
   <tableColumns count="10">
     <tableColumn id="1" name="date"/>
     <tableColumn id="2" name="domain"/>
@@ -5956,6 +5956,1662 @@
         <v>170</v>
       </c>
     </row>
+    <row r="158">
+      <c r="A158" s="2" t="n">
+        <v>46181</v>
+      </c>
+      <c r="B158" t="s">
+        <v>10</v>
+      </c>
+      <c r="C158" t="s">
+        <v>11</v>
+      </c>
+      <c r="D158" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E158" s="3" t="n">
+        <v>63</v>
+      </c>
+      <c r="F158" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G158" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H158" s="3" t="n">
+        <v>68</v>
+      </c>
+      <c r="I158" t="s">
+        <v>15</v>
+      </c>
+      <c r="J158" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="n">
+        <v>46181</v>
+      </c>
+      <c r="B159" t="s">
+        <v>10</v>
+      </c>
+      <c r="C159" t="s">
+        <v>17</v>
+      </c>
+      <c r="D159" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E159" s="3" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="F159" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G159" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H159" s="3" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="I159" t="s">
+        <v>21</v>
+      </c>
+      <c r="J159" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="n">
+        <v>46181</v>
+      </c>
+      <c r="B160" t="s">
+        <v>10</v>
+      </c>
+      <c r="C160" t="s">
+        <v>23</v>
+      </c>
+      <c r="D160" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E160" s="3" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="F160" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G160" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H160" s="3" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="I160" t="s">
+        <v>21</v>
+      </c>
+      <c r="J160" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="n">
+        <v>46181</v>
+      </c>
+      <c r="B161" t="s">
+        <v>10</v>
+      </c>
+      <c r="C161" t="s">
+        <v>26</v>
+      </c>
+      <c r="D161" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E161" s="3" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="F161" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G161" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H161" s="3" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="I161" t="s">
+        <v>30</v>
+      </c>
+      <c r="J161" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="n">
+        <v>46181</v>
+      </c>
+      <c r="B162" t="s">
+        <v>32</v>
+      </c>
+      <c r="C162" t="s">
+        <v>33</v>
+      </c>
+      <c r="D162" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E162" s="3" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="F162" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G162" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H162" s="3" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="I162" t="s">
+        <v>15</v>
+      </c>
+      <c r="J162" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="n">
+        <v>46181</v>
+      </c>
+      <c r="B163" t="s">
+        <v>32</v>
+      </c>
+      <c r="C163" t="s">
+        <v>37</v>
+      </c>
+      <c r="D163" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E163" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="F163" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G163" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H163" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="I163" t="s">
+        <v>30</v>
+      </c>
+      <c r="J163" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="n">
+        <v>46181</v>
+      </c>
+      <c r="B164" t="s">
+        <v>32</v>
+      </c>
+      <c r="C164" t="s">
+        <v>39</v>
+      </c>
+      <c r="D164" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E164" s="3" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="F164" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="G164" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H164" s="3" t="n">
+        <v>54.3</v>
+      </c>
+      <c r="I164" t="s">
+        <v>21</v>
+      </c>
+      <c r="J164" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="n">
+        <v>46181</v>
+      </c>
+      <c r="B165" t="s">
+        <v>32</v>
+      </c>
+      <c r="C165" t="s">
+        <v>44</v>
+      </c>
+      <c r="D165" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E165" s="3" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="F165" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="G165" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H165" s="3" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="I165" t="s">
+        <v>15</v>
+      </c>
+      <c r="J165" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="n">
+        <v>46181</v>
+      </c>
+      <c r="B166" t="s">
+        <v>32</v>
+      </c>
+      <c r="C166" t="s">
+        <v>47</v>
+      </c>
+      <c r="D166" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E166" s="3" t="n">
+        <v>47.9</v>
+      </c>
+      <c r="F166" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G166" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H166" s="3" t="n">
+        <v>47.8</v>
+      </c>
+      <c r="I166" t="s">
+        <v>21</v>
+      </c>
+      <c r="J166" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="n">
+        <v>46181</v>
+      </c>
+      <c r="B167" t="s">
+        <v>32</v>
+      </c>
+      <c r="C167" t="s">
+        <v>50</v>
+      </c>
+      <c r="D167" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E167" s="3" t="n">
+        <v>51.9</v>
+      </c>
+      <c r="F167" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="G167" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H167" s="3" t="n">
+        <v>51</v>
+      </c>
+      <c r="I167" t="s">
+        <v>30</v>
+      </c>
+      <c r="J167" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="n">
+        <v>46181</v>
+      </c>
+      <c r="B168" t="s">
+        <v>32</v>
+      </c>
+      <c r="C168" t="s">
+        <v>53</v>
+      </c>
+      <c r="D168" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E168" s="3" t="n">
+        <v>49.2</v>
+      </c>
+      <c r="F168" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="G168" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H168" s="3" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="I168" t="s">
+        <v>21</v>
+      </c>
+      <c r="J168" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="n">
+        <v>46181</v>
+      </c>
+      <c r="B169" t="s">
+        <v>32</v>
+      </c>
+      <c r="C169" t="s">
+        <v>56</v>
+      </c>
+      <c r="D169" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E169" s="3" t="n">
+        <v>0.063</v>
+      </c>
+      <c r="F169" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="G169" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H169" s="3" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="I169" t="s">
+        <v>30</v>
+      </c>
+      <c r="J169" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="n">
+        <v>46181</v>
+      </c>
+      <c r="B170" t="s">
+        <v>32</v>
+      </c>
+      <c r="C170" t="s">
+        <v>59</v>
+      </c>
+      <c r="D170" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E170" s="3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="F170" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="G170" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H170" s="3" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="I170" t="s">
+        <v>30</v>
+      </c>
+      <c r="J170" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="n">
+        <v>46181</v>
+      </c>
+      <c r="B171" t="s">
+        <v>63</v>
+      </c>
+      <c r="C171" t="s">
+        <v>64</v>
+      </c>
+      <c r="D171" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E171" s="3" t="n">
+        <v>49.6</v>
+      </c>
+      <c r="F171" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="G171" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H171" s="3" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="I171" t="s">
+        <v>15</v>
+      </c>
+      <c r="J171" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="n">
+        <v>46181</v>
+      </c>
+      <c r="B172" t="s">
+        <v>63</v>
+      </c>
+      <c r="C172" t="s">
+        <v>67</v>
+      </c>
+      <c r="D172" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E172" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="F172" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="G172" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="H172" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="I172" t="s">
+        <v>30</v>
+      </c>
+      <c r="J172" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="n">
+        <v>46181</v>
+      </c>
+      <c r="B173" t="s">
+        <v>63</v>
+      </c>
+      <c r="C173" t="s">
+        <v>71</v>
+      </c>
+      <c r="D173" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E173" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="F173" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="G173" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="H173" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="I173" t="s">
+        <v>30</v>
+      </c>
+      <c r="J173" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="n">
+        <v>46181</v>
+      </c>
+      <c r="B174" t="s">
+        <v>63</v>
+      </c>
+      <c r="C174" t="s">
+        <v>73</v>
+      </c>
+      <c r="D174" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E174" s="3" t="n">
+        <v>36.1</v>
+      </c>
+      <c r="F174" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="G174" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H174" s="3" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="I174" t="s">
+        <v>21</v>
+      </c>
+      <c r="J174" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="n">
+        <v>46181</v>
+      </c>
+      <c r="B175" t="s">
+        <v>75</v>
+      </c>
+      <c r="C175" t="s">
+        <v>76</v>
+      </c>
+      <c r="D175" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E175" s="3" t="n">
+        <v>56</v>
+      </c>
+      <c r="F175" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="G175" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H175" s="3" t="n">
+        <v>56.3</v>
+      </c>
+      <c r="I175" t="s">
+        <v>30</v>
+      </c>
+      <c r="J175" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="n">
+        <v>46181</v>
+      </c>
+      <c r="B176" t="s">
+        <v>75</v>
+      </c>
+      <c r="C176" t="s">
+        <v>78</v>
+      </c>
+      <c r="D176" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="E176" s="3" t="n">
+        <v>62.1</v>
+      </c>
+      <c r="F176" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="G176" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="H176" s="3" t="n">
+        <v>60.2</v>
+      </c>
+      <c r="I176" t="s">
+        <v>21</v>
+      </c>
+      <c r="J176" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="n">
+        <v>46181</v>
+      </c>
+      <c r="B177" t="s">
+        <v>75</v>
+      </c>
+      <c r="C177" t="s">
+        <v>83</v>
+      </c>
+      <c r="D177" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="E177" s="3" t="n">
+        <v>60.1</v>
+      </c>
+      <c r="F177" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="G177" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="H177" s="3" t="n">
+        <v>59.3</v>
+      </c>
+      <c r="I177" t="s">
+        <v>30</v>
+      </c>
+      <c r="J177" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="n">
+        <v>46181</v>
+      </c>
+      <c r="B178" t="s">
+        <v>75</v>
+      </c>
+      <c r="C178" t="s">
+        <v>86</v>
+      </c>
+      <c r="D178" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E178" s="3" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="F178" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="G178" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H178" s="3" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="I178" t="s">
+        <v>15</v>
+      </c>
+      <c r="J178" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="n">
+        <v>46181</v>
+      </c>
+      <c r="B179" t="s">
+        <v>75</v>
+      </c>
+      <c r="C179" t="s">
+        <v>89</v>
+      </c>
+      <c r="D179" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="E179" s="3" t="n">
+        <v>169</v>
+      </c>
+      <c r="F179" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="G179" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="H179" s="3" t="n">
+        <v>181</v>
+      </c>
+      <c r="I179" t="s">
+        <v>21</v>
+      </c>
+      <c r="J179" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="n">
+        <v>46181</v>
+      </c>
+      <c r="B180" t="s">
+        <v>75</v>
+      </c>
+      <c r="C180" t="s">
+        <v>94</v>
+      </c>
+      <c r="D180" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E180" s="3" t="n">
+        <v>75</v>
+      </c>
+      <c r="F180" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="G180" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H180" s="3" t="n">
+        <v>73</v>
+      </c>
+      <c r="I180" t="s">
+        <v>21</v>
+      </c>
+      <c r="J180" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="n">
+        <v>46181</v>
+      </c>
+      <c r="B181" t="s">
+        <v>98</v>
+      </c>
+      <c r="C181" t="s">
+        <v>99</v>
+      </c>
+      <c r="D181" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E181" s="3" t="n">
+        <v>62</v>
+      </c>
+      <c r="F181" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="G181" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H181" s="3" t="n">
+        <v>85</v>
+      </c>
+      <c r="I181" t="s">
+        <v>15</v>
+      </c>
+      <c r="J181" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="n">
+        <v>46181</v>
+      </c>
+      <c r="B182" t="s">
+        <v>98</v>
+      </c>
+      <c r="C182" t="s">
+        <v>101</v>
+      </c>
+      <c r="D182" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E182" s="3" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="F182" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="G182" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H182" s="3" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="I182" t="s">
+        <v>30</v>
+      </c>
+      <c r="J182" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="n">
+        <v>46181</v>
+      </c>
+      <c r="B183" t="s">
+        <v>98</v>
+      </c>
+      <c r="C183" t="s">
+        <v>104</v>
+      </c>
+      <c r="D183" s="3"/>
+      <c r="E183" s="3"/>
+      <c r="F183" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="G183" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="H183" s="3" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="I183" t="s">
+        <v>61</v>
+      </c>
+      <c r="J183" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="n">
+        <v>46181</v>
+      </c>
+      <c r="B184" t="s">
+        <v>98</v>
+      </c>
+      <c r="C184" t="s">
+        <v>106</v>
+      </c>
+      <c r="D184" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E184" s="3" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="F184" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="G184" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H184" s="3" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="I184" t="s">
+        <v>21</v>
+      </c>
+      <c r="J184" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="n">
+        <v>46181</v>
+      </c>
+      <c r="B185" t="s">
+        <v>108</v>
+      </c>
+      <c r="C185" t="s">
+        <v>109</v>
+      </c>
+      <c r="D185" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E185" s="3" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="F185" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="G185" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H185" s="3" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="I185" t="s">
+        <v>15</v>
+      </c>
+      <c r="J185" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="n">
+        <v>46181</v>
+      </c>
+      <c r="B186" t="s">
+        <v>108</v>
+      </c>
+      <c r="C186" t="s">
+        <v>111</v>
+      </c>
+      <c r="D186" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E186" s="3" t="n">
+        <v>69.8</v>
+      </c>
+      <c r="F186" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="G186" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H186" s="3" t="n">
+        <v>74.3</v>
+      </c>
+      <c r="I186" t="s">
+        <v>15</v>
+      </c>
+      <c r="J186" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="n">
+        <v>46181</v>
+      </c>
+      <c r="B187" t="s">
+        <v>108</v>
+      </c>
+      <c r="C187" t="s">
+        <v>114</v>
+      </c>
+      <c r="D187" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E187" s="3" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="F187" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="G187" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H187" s="3" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="I187" t="s">
+        <v>15</v>
+      </c>
+      <c r="J187" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="n">
+        <v>46181</v>
+      </c>
+      <c r="B188" t="s">
+        <v>108</v>
+      </c>
+      <c r="C188" t="s">
+        <v>117</v>
+      </c>
+      <c r="D188" s="3"/>
+      <c r="E188" s="3"/>
+      <c r="F188" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G188" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H188" s="3" t="n">
+        <v>69</v>
+      </c>
+      <c r="I188" t="s">
+        <v>61</v>
+      </c>
+      <c r="J188" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="n">
+        <v>46181</v>
+      </c>
+      <c r="B189" t="s">
+        <v>108</v>
+      </c>
+      <c r="C189" t="s">
+        <v>119</v>
+      </c>
+      <c r="D189" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="E189" s="3" t="n">
+        <v>61.27</v>
+      </c>
+      <c r="F189" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G189" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H189" s="3" t="n">
+        <v>62.21</v>
+      </c>
+      <c r="I189" t="s">
+        <v>30</v>
+      </c>
+      <c r="J189" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="n">
+        <v>46181</v>
+      </c>
+      <c r="B190" t="s">
+        <v>108</v>
+      </c>
+      <c r="C190" t="s">
+        <v>121</v>
+      </c>
+      <c r="D190" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E190" s="3" t="n">
+        <v>92.8</v>
+      </c>
+      <c r="F190" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G190" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H190" s="3" t="n">
+        <v>99.5</v>
+      </c>
+      <c r="I190" t="s">
+        <v>15</v>
+      </c>
+      <c r="J190" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="n">
+        <v>46181</v>
+      </c>
+      <c r="B191" t="s">
+        <v>108</v>
+      </c>
+      <c r="C191" t="s">
+        <v>123</v>
+      </c>
+      <c r="D191" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="E191" s="3" t="n">
+        <v>96.3</v>
+      </c>
+      <c r="F191" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G191" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H191" s="3" t="n">
+        <v>104.4</v>
+      </c>
+      <c r="I191" t="s">
+        <v>15</v>
+      </c>
+      <c r="J191" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="n">
+        <v>46181</v>
+      </c>
+      <c r="B192" t="s">
+        <v>108</v>
+      </c>
+      <c r="C192" t="s">
+        <v>126</v>
+      </c>
+      <c r="D192" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E192" s="3" t="n">
+        <v>1170.4</v>
+      </c>
+      <c r="F192" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G192" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H192" s="3" t="n">
+        <v>1000.7</v>
+      </c>
+      <c r="I192" t="s">
+        <v>21</v>
+      </c>
+      <c r="J192" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="n">
+        <v>46181</v>
+      </c>
+      <c r="B193" t="s">
+        <v>108</v>
+      </c>
+      <c r="C193" t="s">
+        <v>128</v>
+      </c>
+      <c r="D193" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E193" s="3" t="n">
+        <v>76.3</v>
+      </c>
+      <c r="F193" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="G193" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H193" s="3" t="n">
+        <v>80.4</v>
+      </c>
+      <c r="I193" t="s">
+        <v>15</v>
+      </c>
+      <c r="J193" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="n">
+        <v>46181</v>
+      </c>
+      <c r="B194" t="s">
+        <v>131</v>
+      </c>
+      <c r="C194" t="s">
+        <v>132</v>
+      </c>
+      <c r="D194" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E194" s="3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="F194" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="G194" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="H194" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I194" t="s">
+        <v>30</v>
+      </c>
+      <c r="J194" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="n">
+        <v>46181</v>
+      </c>
+      <c r="B195" t="s">
+        <v>131</v>
+      </c>
+      <c r="C195" t="s">
+        <v>134</v>
+      </c>
+      <c r="D195" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E195" s="3" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="F195" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="G195" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="H195" s="3" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="I195" t="s">
+        <v>30</v>
+      </c>
+      <c r="J195" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="n">
+        <v>46181</v>
+      </c>
+      <c r="B196" t="s">
+        <v>131</v>
+      </c>
+      <c r="C196" t="s">
+        <v>136</v>
+      </c>
+      <c r="D196" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="E196" s="3" t="n">
+        <v>193</v>
+      </c>
+      <c r="F196" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="G196" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H196" s="3" t="n">
+        <v>189</v>
+      </c>
+      <c r="I196" t="s">
+        <v>30</v>
+      </c>
+      <c r="J196" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="n">
+        <v>46181</v>
+      </c>
+      <c r="B197" t="s">
+        <v>131</v>
+      </c>
+      <c r="C197" t="s">
+        <v>140</v>
+      </c>
+      <c r="D197" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E197" s="3" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="F197" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="G197" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H197" s="3" t="n">
+        <v>40.7</v>
+      </c>
+      <c r="I197" t="s">
+        <v>21</v>
+      </c>
+      <c r="J197" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="n">
+        <v>46181</v>
+      </c>
+      <c r="B198" t="s">
+        <v>131</v>
+      </c>
+      <c r="C198" t="s">
+        <v>142</v>
+      </c>
+      <c r="D198" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E198" s="3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="F198" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="G198" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="H198" s="3" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="I198" t="s">
+        <v>30</v>
+      </c>
+      <c r="J198" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="n">
+        <v>46181</v>
+      </c>
+      <c r="B199" t="s">
+        <v>145</v>
+      </c>
+      <c r="C199" t="s">
+        <v>146</v>
+      </c>
+      <c r="D199" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E199" s="3" t="n">
+        <v>68.4</v>
+      </c>
+      <c r="F199" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G199" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H199" s="3" t="n">
+        <v>69.2</v>
+      </c>
+      <c r="I199" t="s">
+        <v>30</v>
+      </c>
+      <c r="J199" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="n">
+        <v>46181</v>
+      </c>
+      <c r="B200" t="s">
+        <v>145</v>
+      </c>
+      <c r="C200" t="s">
+        <v>148</v>
+      </c>
+      <c r="D200" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E200" s="3" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="F200" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="G200" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H200" s="3" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="I200" t="s">
+        <v>15</v>
+      </c>
+      <c r="J200" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="2" t="n">
+        <v>46181</v>
+      </c>
+      <c r="B201" t="s">
+        <v>145</v>
+      </c>
+      <c r="C201" t="s">
+        <v>150</v>
+      </c>
+      <c r="D201" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="E201" s="3" t="n">
+        <v>47</v>
+      </c>
+      <c r="F201" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="G201" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H201" s="3" t="n">
+        <v>46</v>
+      </c>
+      <c r="I201" t="s">
+        <v>30</v>
+      </c>
+      <c r="J201" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="2" t="n">
+        <v>46181</v>
+      </c>
+      <c r="B202" t="s">
+        <v>152</v>
+      </c>
+      <c r="C202" t="s">
+        <v>153</v>
+      </c>
+      <c r="D202" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E202" s="3" t="n">
+        <v>90</v>
+      </c>
+      <c r="F202" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="G202" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H202" s="3" t="n">
+        <v>91</v>
+      </c>
+      <c r="I202" t="s">
+        <v>30</v>
+      </c>
+      <c r="J202" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="2" t="n">
+        <v>46181</v>
+      </c>
+      <c r="B203" t="s">
+        <v>152</v>
+      </c>
+      <c r="C203" t="s">
+        <v>154</v>
+      </c>
+      <c r="D203" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E203" s="3" t="n">
+        <v>10135</v>
+      </c>
+      <c r="F203" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="G203" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H203" s="3" t="n">
+        <v>10855</v>
+      </c>
+      <c r="I203" t="s">
+        <v>21</v>
+      </c>
+      <c r="J203" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="n">
+        <v>46181</v>
+      </c>
+      <c r="B204" t="s">
+        <v>152</v>
+      </c>
+      <c r="C204" t="s">
+        <v>156</v>
+      </c>
+      <c r="D204" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E204" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F204" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="G204" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="H204" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="I204" t="s">
+        <v>30</v>
+      </c>
+      <c r="J204" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="2" t="n">
+        <v>46181</v>
+      </c>
+      <c r="B205" t="s">
+        <v>152</v>
+      </c>
+      <c r="C205" t="s">
+        <v>159</v>
+      </c>
+      <c r="D205" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="E205" s="3" t="n">
+        <v>30288</v>
+      </c>
+      <c r="F205" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="G205" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H205" s="3" t="n">
+        <v>37635</v>
+      </c>
+      <c r="I205" t="s">
+        <v>21</v>
+      </c>
+      <c r="J205" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="2" t="n">
+        <v>46181</v>
+      </c>
+      <c r="B206" t="s">
+        <v>161</v>
+      </c>
+      <c r="C206" t="s">
+        <v>162</v>
+      </c>
+      <c r="D206" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E206" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="F206" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="G206" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H206" s="3" t="n">
+        <v>46.7</v>
+      </c>
+      <c r="I206" t="s">
+        <v>15</v>
+      </c>
+      <c r="J206" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="2" t="n">
+        <v>46181</v>
+      </c>
+      <c r="B207" t="s">
+        <v>161</v>
+      </c>
+      <c r="C207" t="s">
+        <v>164</v>
+      </c>
+      <c r="D207" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E207" s="3" t="n">
+        <v>78.6</v>
+      </c>
+      <c r="F207" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="G207" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H207" s="3" t="n">
+        <v>76.1</v>
+      </c>
+      <c r="I207" t="s">
+        <v>21</v>
+      </c>
+      <c r="J207" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="2" t="n">
+        <v>46181</v>
+      </c>
+      <c r="B208" t="s">
+        <v>161</v>
+      </c>
+      <c r="C208" t="s">
+        <v>165</v>
+      </c>
+      <c r="D208" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E208" s="3" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="F208" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="G208" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H208" s="3" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="I208" t="s">
+        <v>30</v>
+      </c>
+      <c r="J208" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="2" t="n">
+        <v>46181</v>
+      </c>
+      <c r="B209" t="s">
+        <v>161</v>
+      </c>
+      <c r="C209" t="s">
+        <v>168</v>
+      </c>
+      <c r="D209" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E209" s="3" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="F209" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="G209" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H209" s="3" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="I209" t="s">
+        <v>30</v>
+      </c>
+      <c r="J209" t="s">
+        <v>170</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/indicator-performance-table.xlsx
+++ b/indicator-performance-table.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="198">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -600,6 +600,12 @@
   </si>
   <si>
     <t xml:space="preserve">2020-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026</t>
   </si>
 </sst>
 </file>
@@ -659,8 +665,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:J209" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:J209"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:J261" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:J261"/>
   <tableColumns count="10">
     <tableColumn id="1" name="date"/>
     <tableColumn id="2" name="domain"/>
@@ -7612,6 +7618,1662 @@
         <v>170</v>
       </c>
     </row>
+    <row r="210">
+      <c r="A210" s="2" t="n">
+        <v>46188</v>
+      </c>
+      <c r="B210" t="s">
+        <v>10</v>
+      </c>
+      <c r="C210" t="s">
+        <v>11</v>
+      </c>
+      <c r="D210" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E210" s="3" t="n">
+        <v>63</v>
+      </c>
+      <c r="F210" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G210" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H210" s="3" t="n">
+        <v>68</v>
+      </c>
+      <c r="I210" t="s">
+        <v>15</v>
+      </c>
+      <c r="J210" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="2" t="n">
+        <v>46188</v>
+      </c>
+      <c r="B211" t="s">
+        <v>10</v>
+      </c>
+      <c r="C211" t="s">
+        <v>17</v>
+      </c>
+      <c r="D211" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E211" s="3" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="F211" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G211" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H211" s="3" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="I211" t="s">
+        <v>21</v>
+      </c>
+      <c r="J211" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="2" t="n">
+        <v>46188</v>
+      </c>
+      <c r="B212" t="s">
+        <v>10</v>
+      </c>
+      <c r="C212" t="s">
+        <v>23</v>
+      </c>
+      <c r="D212" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E212" s="3" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="F212" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G212" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H212" s="3" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="I212" t="s">
+        <v>21</v>
+      </c>
+      <c r="J212" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="2" t="n">
+        <v>46188</v>
+      </c>
+      <c r="B213" t="s">
+        <v>10</v>
+      </c>
+      <c r="C213" t="s">
+        <v>26</v>
+      </c>
+      <c r="D213" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E213" s="3" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="F213" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G213" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H213" s="3" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="I213" t="s">
+        <v>30</v>
+      </c>
+      <c r="J213" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="2" t="n">
+        <v>46188</v>
+      </c>
+      <c r="B214" t="s">
+        <v>32</v>
+      </c>
+      <c r="C214" t="s">
+        <v>33</v>
+      </c>
+      <c r="D214" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E214" s="3" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="F214" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G214" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H214" s="3" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="I214" t="s">
+        <v>15</v>
+      </c>
+      <c r="J214" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="2" t="n">
+        <v>46188</v>
+      </c>
+      <c r="B215" t="s">
+        <v>32</v>
+      </c>
+      <c r="C215" t="s">
+        <v>37</v>
+      </c>
+      <c r="D215" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E215" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="F215" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G215" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H215" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="I215" t="s">
+        <v>21</v>
+      </c>
+      <c r="J215" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="2" t="n">
+        <v>46188</v>
+      </c>
+      <c r="B216" t="s">
+        <v>32</v>
+      </c>
+      <c r="C216" t="s">
+        <v>39</v>
+      </c>
+      <c r="D216" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E216" s="3" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="F216" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="G216" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="H216" s="3" t="n">
+        <v>52</v>
+      </c>
+      <c r="I216" t="s">
+        <v>21</v>
+      </c>
+      <c r="J216" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="2" t="n">
+        <v>46188</v>
+      </c>
+      <c r="B217" t="s">
+        <v>32</v>
+      </c>
+      <c r="C217" t="s">
+        <v>44</v>
+      </c>
+      <c r="D217" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E217" s="3" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="F217" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="G217" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H217" s="3" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="I217" t="s">
+        <v>15</v>
+      </c>
+      <c r="J217" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="2" t="n">
+        <v>46188</v>
+      </c>
+      <c r="B218" t="s">
+        <v>32</v>
+      </c>
+      <c r="C218" t="s">
+        <v>47</v>
+      </c>
+      <c r="D218" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E218" s="3" t="n">
+        <v>48.2</v>
+      </c>
+      <c r="F218" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G218" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="H218" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="I218" t="s">
+        <v>21</v>
+      </c>
+      <c r="J218" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="2" t="n">
+        <v>46188</v>
+      </c>
+      <c r="B219" t="s">
+        <v>32</v>
+      </c>
+      <c r="C219" t="s">
+        <v>50</v>
+      </c>
+      <c r="D219" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E219" s="3" t="n">
+        <v>51.9</v>
+      </c>
+      <c r="F219" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="G219" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H219" s="3" t="n">
+        <v>51</v>
+      </c>
+      <c r="I219" t="s">
+        <v>30</v>
+      </c>
+      <c r="J219" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="2" t="n">
+        <v>46188</v>
+      </c>
+      <c r="B220" t="s">
+        <v>32</v>
+      </c>
+      <c r="C220" t="s">
+        <v>53</v>
+      </c>
+      <c r="D220" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E220" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="F220" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="G220" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H220" s="3" t="n">
+        <v>47</v>
+      </c>
+      <c r="I220" t="s">
+        <v>21</v>
+      </c>
+      <c r="J220" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="2" t="n">
+        <v>46188</v>
+      </c>
+      <c r="B221" t="s">
+        <v>32</v>
+      </c>
+      <c r="C221" t="s">
+        <v>56</v>
+      </c>
+      <c r="D221" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E221" s="3" t="n">
+        <v>0.063</v>
+      </c>
+      <c r="F221" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="G221" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H221" s="3" t="n">
+        <v>0.07</v>
+      </c>
+      <c r="I221" t="s">
+        <v>30</v>
+      </c>
+      <c r="J221" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="2" t="n">
+        <v>46188</v>
+      </c>
+      <c r="B222" t="s">
+        <v>32</v>
+      </c>
+      <c r="C222" t="s">
+        <v>59</v>
+      </c>
+      <c r="D222" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E222" s="3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="F222" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="G222" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H222" s="3" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="I222" t="s">
+        <v>30</v>
+      </c>
+      <c r="J222" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="2" t="n">
+        <v>46188</v>
+      </c>
+      <c r="B223" t="s">
+        <v>63</v>
+      </c>
+      <c r="C223" t="s">
+        <v>64</v>
+      </c>
+      <c r="D223" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E223" s="3" t="n">
+        <v>49.6</v>
+      </c>
+      <c r="F223" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="G223" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H223" s="3" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="I223" t="s">
+        <v>15</v>
+      </c>
+      <c r="J223" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="2" t="n">
+        <v>46188</v>
+      </c>
+      <c r="B224" t="s">
+        <v>63</v>
+      </c>
+      <c r="C224" t="s">
+        <v>67</v>
+      </c>
+      <c r="D224" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E224" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="F224" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="G224" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="H224" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="I224" t="s">
+        <v>30</v>
+      </c>
+      <c r="J224" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="2" t="n">
+        <v>46188</v>
+      </c>
+      <c r="B225" t="s">
+        <v>63</v>
+      </c>
+      <c r="C225" t="s">
+        <v>71</v>
+      </c>
+      <c r="D225" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E225" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="F225" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="G225" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="H225" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="I225" t="s">
+        <v>30</v>
+      </c>
+      <c r="J225" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="2" t="n">
+        <v>46188</v>
+      </c>
+      <c r="B226" t="s">
+        <v>63</v>
+      </c>
+      <c r="C226" t="s">
+        <v>73</v>
+      </c>
+      <c r="D226" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E226" s="3" t="n">
+        <v>36.1</v>
+      </c>
+      <c r="F226" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="G226" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H226" s="3" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="I226" t="s">
+        <v>21</v>
+      </c>
+      <c r="J226" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="2" t="n">
+        <v>46188</v>
+      </c>
+      <c r="B227" t="s">
+        <v>75</v>
+      </c>
+      <c r="C227" t="s">
+        <v>76</v>
+      </c>
+      <c r="D227" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E227" s="3" t="n">
+        <v>56</v>
+      </c>
+      <c r="F227" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="G227" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H227" s="3" t="n">
+        <v>56.3</v>
+      </c>
+      <c r="I227" t="s">
+        <v>30</v>
+      </c>
+      <c r="J227" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="2" t="n">
+        <v>46188</v>
+      </c>
+      <c r="B228" t="s">
+        <v>75</v>
+      </c>
+      <c r="C228" t="s">
+        <v>78</v>
+      </c>
+      <c r="D228" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="E228" s="3" t="n">
+        <v>62.1</v>
+      </c>
+      <c r="F228" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="G228" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="H228" s="3" t="n">
+        <v>60.2</v>
+      </c>
+      <c r="I228" t="s">
+        <v>21</v>
+      </c>
+      <c r="J228" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="2" t="n">
+        <v>46188</v>
+      </c>
+      <c r="B229" t="s">
+        <v>75</v>
+      </c>
+      <c r="C229" t="s">
+        <v>83</v>
+      </c>
+      <c r="D229" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="E229" s="3" t="n">
+        <v>60.1</v>
+      </c>
+      <c r="F229" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="G229" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="H229" s="3" t="n">
+        <v>59.3</v>
+      </c>
+      <c r="I229" t="s">
+        <v>30</v>
+      </c>
+      <c r="J229" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="2" t="n">
+        <v>46188</v>
+      </c>
+      <c r="B230" t="s">
+        <v>75</v>
+      </c>
+      <c r="C230" t="s">
+        <v>86</v>
+      </c>
+      <c r="D230" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E230" s="3" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="F230" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="G230" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H230" s="3" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="I230" t="s">
+        <v>15</v>
+      </c>
+      <c r="J230" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="2" t="n">
+        <v>46188</v>
+      </c>
+      <c r="B231" t="s">
+        <v>75</v>
+      </c>
+      <c r="C231" t="s">
+        <v>89</v>
+      </c>
+      <c r="D231" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="E231" s="3" t="n">
+        <v>169</v>
+      </c>
+      <c r="F231" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="G231" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="H231" s="3" t="n">
+        <v>181</v>
+      </c>
+      <c r="I231" t="s">
+        <v>21</v>
+      </c>
+      <c r="J231" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="2" t="n">
+        <v>46188</v>
+      </c>
+      <c r="B232" t="s">
+        <v>75</v>
+      </c>
+      <c r="C232" t="s">
+        <v>94</v>
+      </c>
+      <c r="D232" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E232" s="3" t="n">
+        <v>75</v>
+      </c>
+      <c r="F232" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="G232" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H232" s="3" t="n">
+        <v>73</v>
+      </c>
+      <c r="I232" t="s">
+        <v>21</v>
+      </c>
+      <c r="J232" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="2" t="n">
+        <v>46188</v>
+      </c>
+      <c r="B233" t="s">
+        <v>98</v>
+      </c>
+      <c r="C233" t="s">
+        <v>99</v>
+      </c>
+      <c r="D233" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E233" s="3" t="n">
+        <v>62</v>
+      </c>
+      <c r="F233" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="G233" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H233" s="3" t="n">
+        <v>85</v>
+      </c>
+      <c r="I233" t="s">
+        <v>15</v>
+      </c>
+      <c r="J233" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="2" t="n">
+        <v>46188</v>
+      </c>
+      <c r="B234" t="s">
+        <v>98</v>
+      </c>
+      <c r="C234" t="s">
+        <v>101</v>
+      </c>
+      <c r="D234" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E234" s="3" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="F234" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="G234" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H234" s="3" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="I234" t="s">
+        <v>30</v>
+      </c>
+      <c r="J234" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="2" t="n">
+        <v>46188</v>
+      </c>
+      <c r="B235" t="s">
+        <v>98</v>
+      </c>
+      <c r="C235" t="s">
+        <v>104</v>
+      </c>
+      <c r="D235" s="3"/>
+      <c r="E235" s="3"/>
+      <c r="F235" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="G235" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="H235" s="3" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="I235" t="s">
+        <v>61</v>
+      </c>
+      <c r="J235" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="2" t="n">
+        <v>46188</v>
+      </c>
+      <c r="B236" t="s">
+        <v>98</v>
+      </c>
+      <c r="C236" t="s">
+        <v>106</v>
+      </c>
+      <c r="D236" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E236" s="3" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="F236" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="G236" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H236" s="3" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="I236" t="s">
+        <v>21</v>
+      </c>
+      <c r="J236" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="2" t="n">
+        <v>46188</v>
+      </c>
+      <c r="B237" t="s">
+        <v>108</v>
+      </c>
+      <c r="C237" t="s">
+        <v>109</v>
+      </c>
+      <c r="D237" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E237" s="3" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="F237" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="G237" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H237" s="3" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="I237" t="s">
+        <v>15</v>
+      </c>
+      <c r="J237" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="2" t="n">
+        <v>46188</v>
+      </c>
+      <c r="B238" t="s">
+        <v>108</v>
+      </c>
+      <c r="C238" t="s">
+        <v>111</v>
+      </c>
+      <c r="D238" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E238" s="3" t="n">
+        <v>69.8</v>
+      </c>
+      <c r="F238" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="G238" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H238" s="3" t="n">
+        <v>74.3</v>
+      </c>
+      <c r="I238" t="s">
+        <v>15</v>
+      </c>
+      <c r="J238" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="2" t="n">
+        <v>46188</v>
+      </c>
+      <c r="B239" t="s">
+        <v>108</v>
+      </c>
+      <c r="C239" t="s">
+        <v>114</v>
+      </c>
+      <c r="D239" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E239" s="3" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="F239" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="G239" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H239" s="3" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="I239" t="s">
+        <v>15</v>
+      </c>
+      <c r="J239" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="2" t="n">
+        <v>46188</v>
+      </c>
+      <c r="B240" t="s">
+        <v>108</v>
+      </c>
+      <c r="C240" t="s">
+        <v>117</v>
+      </c>
+      <c r="D240" s="3"/>
+      <c r="E240" s="3"/>
+      <c r="F240" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G240" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H240" s="3" t="n">
+        <v>69</v>
+      </c>
+      <c r="I240" t="s">
+        <v>61</v>
+      </c>
+      <c r="J240" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="2" t="n">
+        <v>46188</v>
+      </c>
+      <c r="B241" t="s">
+        <v>108</v>
+      </c>
+      <c r="C241" t="s">
+        <v>119</v>
+      </c>
+      <c r="D241" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="E241" s="3" t="n">
+        <v>61.27</v>
+      </c>
+      <c r="F241" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G241" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H241" s="3" t="n">
+        <v>62.21</v>
+      </c>
+      <c r="I241" t="s">
+        <v>30</v>
+      </c>
+      <c r="J241" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="2" t="n">
+        <v>46188</v>
+      </c>
+      <c r="B242" t="s">
+        <v>108</v>
+      </c>
+      <c r="C242" t="s">
+        <v>121</v>
+      </c>
+      <c r="D242" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E242" s="3" t="n">
+        <v>92.8</v>
+      </c>
+      <c r="F242" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G242" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H242" s="3" t="n">
+        <v>99.5</v>
+      </c>
+      <c r="I242" t="s">
+        <v>15</v>
+      </c>
+      <c r="J242" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="2" t="n">
+        <v>46188</v>
+      </c>
+      <c r="B243" t="s">
+        <v>108</v>
+      </c>
+      <c r="C243" t="s">
+        <v>123</v>
+      </c>
+      <c r="D243" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="E243" s="3" t="n">
+        <v>96.3</v>
+      </c>
+      <c r="F243" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G243" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H243" s="3" t="n">
+        <v>104.4</v>
+      </c>
+      <c r="I243" t="s">
+        <v>15</v>
+      </c>
+      <c r="J243" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="2" t="n">
+        <v>46188</v>
+      </c>
+      <c r="B244" t="s">
+        <v>108</v>
+      </c>
+      <c r="C244" t="s">
+        <v>126</v>
+      </c>
+      <c r="D244" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E244" s="3" t="n">
+        <v>1170.4</v>
+      </c>
+      <c r="F244" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G244" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H244" s="3" t="n">
+        <v>1000.7</v>
+      </c>
+      <c r="I244" t="s">
+        <v>21</v>
+      </c>
+      <c r="J244" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="2" t="n">
+        <v>46188</v>
+      </c>
+      <c r="B245" t="s">
+        <v>108</v>
+      </c>
+      <c r="C245" t="s">
+        <v>128</v>
+      </c>
+      <c r="D245" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E245" s="3" t="n">
+        <v>76.3</v>
+      </c>
+      <c r="F245" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="G245" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H245" s="3" t="n">
+        <v>80.4</v>
+      </c>
+      <c r="I245" t="s">
+        <v>15</v>
+      </c>
+      <c r="J245" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="2" t="n">
+        <v>46188</v>
+      </c>
+      <c r="B246" t="s">
+        <v>131</v>
+      </c>
+      <c r="C246" t="s">
+        <v>132</v>
+      </c>
+      <c r="D246" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E246" s="3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="F246" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="G246" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="H246" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I246" t="s">
+        <v>30</v>
+      </c>
+      <c r="J246" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="2" t="n">
+        <v>46188</v>
+      </c>
+      <c r="B247" t="s">
+        <v>131</v>
+      </c>
+      <c r="C247" t="s">
+        <v>134</v>
+      </c>
+      <c r="D247" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E247" s="3" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="F247" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="G247" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="H247" s="3" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="I247" t="s">
+        <v>30</v>
+      </c>
+      <c r="J247" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="2" t="n">
+        <v>46188</v>
+      </c>
+      <c r="B248" t="s">
+        <v>131</v>
+      </c>
+      <c r="C248" t="s">
+        <v>136</v>
+      </c>
+      <c r="D248" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="E248" s="3" t="n">
+        <v>193</v>
+      </c>
+      <c r="F248" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="G248" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H248" s="3" t="n">
+        <v>189</v>
+      </c>
+      <c r="I248" t="s">
+        <v>30</v>
+      </c>
+      <c r="J248" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="2" t="n">
+        <v>46188</v>
+      </c>
+      <c r="B249" t="s">
+        <v>131</v>
+      </c>
+      <c r="C249" t="s">
+        <v>140</v>
+      </c>
+      <c r="D249" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E249" s="3" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="F249" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="G249" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H249" s="3" t="n">
+        <v>40.7</v>
+      </c>
+      <c r="I249" t="s">
+        <v>21</v>
+      </c>
+      <c r="J249" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="2" t="n">
+        <v>46188</v>
+      </c>
+      <c r="B250" t="s">
+        <v>131</v>
+      </c>
+      <c r="C250" t="s">
+        <v>142</v>
+      </c>
+      <c r="D250" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E250" s="3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="F250" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="G250" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="H250" s="3" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="I250" t="s">
+        <v>30</v>
+      </c>
+      <c r="J250" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="2" t="n">
+        <v>46188</v>
+      </c>
+      <c r="B251" t="s">
+        <v>145</v>
+      </c>
+      <c r="C251" t="s">
+        <v>146</v>
+      </c>
+      <c r="D251" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E251" s="3" t="n">
+        <v>68.4</v>
+      </c>
+      <c r="F251" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G251" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H251" s="3" t="n">
+        <v>69.2</v>
+      </c>
+      <c r="I251" t="s">
+        <v>30</v>
+      </c>
+      <c r="J251" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="2" t="n">
+        <v>46188</v>
+      </c>
+      <c r="B252" t="s">
+        <v>145</v>
+      </c>
+      <c r="C252" t="s">
+        <v>148</v>
+      </c>
+      <c r="D252" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E252" s="3" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="F252" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="G252" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H252" s="3" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="I252" t="s">
+        <v>15</v>
+      </c>
+      <c r="J252" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="2" t="n">
+        <v>46188</v>
+      </c>
+      <c r="B253" t="s">
+        <v>145</v>
+      </c>
+      <c r="C253" t="s">
+        <v>150</v>
+      </c>
+      <c r="D253" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="E253" s="3" t="n">
+        <v>47</v>
+      </c>
+      <c r="F253" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="G253" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H253" s="3" t="n">
+        <v>46</v>
+      </c>
+      <c r="I253" t="s">
+        <v>30</v>
+      </c>
+      <c r="J253" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="2" t="n">
+        <v>46188</v>
+      </c>
+      <c r="B254" t="s">
+        <v>152</v>
+      </c>
+      <c r="C254" t="s">
+        <v>153</v>
+      </c>
+      <c r="D254" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E254" s="3" t="n">
+        <v>90</v>
+      </c>
+      <c r="F254" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="G254" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H254" s="3" t="n">
+        <v>91</v>
+      </c>
+      <c r="I254" t="s">
+        <v>30</v>
+      </c>
+      <c r="J254" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="2" t="n">
+        <v>46188</v>
+      </c>
+      <c r="B255" t="s">
+        <v>152</v>
+      </c>
+      <c r="C255" t="s">
+        <v>154</v>
+      </c>
+      <c r="D255" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E255" s="3" t="n">
+        <v>10135</v>
+      </c>
+      <c r="F255" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="G255" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H255" s="3" t="n">
+        <v>10855</v>
+      </c>
+      <c r="I255" t="s">
+        <v>21</v>
+      </c>
+      <c r="J255" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="2" t="n">
+        <v>46188</v>
+      </c>
+      <c r="B256" t="s">
+        <v>152</v>
+      </c>
+      <c r="C256" t="s">
+        <v>156</v>
+      </c>
+      <c r="D256" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E256" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F256" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="G256" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="H256" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="I256" t="s">
+        <v>30</v>
+      </c>
+      <c r="J256" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="2" t="n">
+        <v>46188</v>
+      </c>
+      <c r="B257" t="s">
+        <v>152</v>
+      </c>
+      <c r="C257" t="s">
+        <v>159</v>
+      </c>
+      <c r="D257" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="E257" s="3" t="n">
+        <v>30288</v>
+      </c>
+      <c r="F257" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="G257" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H257" s="3" t="n">
+        <v>37635</v>
+      </c>
+      <c r="I257" t="s">
+        <v>21</v>
+      </c>
+      <c r="J257" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="2" t="n">
+        <v>46188</v>
+      </c>
+      <c r="B258" t="s">
+        <v>161</v>
+      </c>
+      <c r="C258" t="s">
+        <v>162</v>
+      </c>
+      <c r="D258" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E258" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="F258" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="G258" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H258" s="3" t="n">
+        <v>46.7</v>
+      </c>
+      <c r="I258" t="s">
+        <v>15</v>
+      </c>
+      <c r="J258" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="2" t="n">
+        <v>46188</v>
+      </c>
+      <c r="B259" t="s">
+        <v>161</v>
+      </c>
+      <c r="C259" t="s">
+        <v>164</v>
+      </c>
+      <c r="D259" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E259" s="3" t="n">
+        <v>78.6</v>
+      </c>
+      <c r="F259" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="G259" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H259" s="3" t="n">
+        <v>76.1</v>
+      </c>
+      <c r="I259" t="s">
+        <v>21</v>
+      </c>
+      <c r="J259" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="2" t="n">
+        <v>46188</v>
+      </c>
+      <c r="B260" t="s">
+        <v>161</v>
+      </c>
+      <c r="C260" t="s">
+        <v>165</v>
+      </c>
+      <c r="D260" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E260" s="3" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="F260" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="G260" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H260" s="3" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="I260" t="s">
+        <v>30</v>
+      </c>
+      <c r="J260" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="2" t="n">
+        <v>46188</v>
+      </c>
+      <c r="B261" t="s">
+        <v>161</v>
+      </c>
+      <c r="C261" t="s">
+        <v>168</v>
+      </c>
+      <c r="D261" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E261" s="3" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="F261" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="G261" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H261" s="3" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="I261" t="s">
+        <v>30</v>
+      </c>
+      <c r="J261" t="s">
+        <v>170</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/indicator-performance-table.xlsx
+++ b/indicator-performance-table.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="218">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -606,13 +606,74 @@
   </si>
   <si>
     <t xml:space="preserve">2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In 2023, the percentage point gap between the percentage of babies found to be small for gestational age for those living in the most and least deprived areas was 6.1 compared with 6.4 in 2019. The change was not statistically significant.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In 2025, the mean nitrogen dioxide level was 27.2μg/m3. NO2 levels have shown a gradual reducing trend from 2011 to 2019. Emission dipped in 2020 to 24.3μg/m3 coinciding with restrictions implemented in response to the Covid-19 pandemic. From 2021 to 2024, emission levels have remained at a similar concentration with an increase to  27.2μg/m3 recorded in the most recent year.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ten water bodies (40 per cent) have been assessed at good or better ecological status in 2025. Excessive levels of nutrients were responsible for 40 per cent of water bodies not achieving good ecological status. Specific pollutants such as the pesticide permethrin are also elements responsible for water bodies failing to achieve good ecological status. All of the water bodies that failed to achieve good status were either transitional (estuarine) waters or coastal sea loughs suggesting catchment-based point and diffuse inputs to these waters.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In 2025/26 52.0 per cent of features within protected sites were in favourable condition which is lower than the 54.8 per cent in favourable condition in 2019/20. Restoring features that are currently in unfavourable condition to favourable condition can take a long time. It should be noted that NIEA has commenced a programme of more detailed Common Standards Monitoring for terrestrial species features which continued into 2025/26. Reporting on some species feature assemblages or groups is now more closely aligned to the niche habitat requirements of those species groups. These changes are in line with Common Standards Monitoring recommendations and has resulted in the number of reported features increasing.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.216c</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In 2024, greenhouse gas emissions remained at the same level as 2023, following the reductions seen in previous years, and continue to be below base year levels.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The indicator shows that the percentage of households with accessible natural space within 400 metres has decreased since the comparision year 2023. 48.0 per cent of households are within 400m of greenspace &gt;2ha, and off-road trails in 2026.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generation of renewable electricity as a proportion of gross final electricity consumption rose from 42% in 2021 to 47% in 2025, with an average of 46% over the 5 year period 2021-2025. Between 2021 and 2025, electricity consumption fell by approximately 8%, while renewable generation only increased by around 3% in the same time period.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Levels of soluble reactive phosphorus (SRP) in the 93 Surveillance Rivers have remained similar with 0.07 mg/l reported in 2025 compared to 0.063 mg/l reported in 2019. Over the longer term, levels of soluble reactive phosphorus in the 93 Surveillance Rivers have increased from the low of 0.047 mg/l reported in 2012.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In 2024/25, 18% of respondents had a high GHQ12 score, which could indicate a mental health problem, compared with 21% in 2021/22. The proportion of males (15%) with a high GHQ12 score is similar to 2021/22, while for females it fell from 25% in 2021/22 to 20% in 2024/25.  Considering the longer term trend, the proportion scoring highly is down from 20% in 2010/11. There was a significant worsening during the pandemic, however findings have returned to pre-pandemic levels. There are differences between subgroups of the population and a consistent gap remains between the most and least deprived areas. Further information on how to interpret the survey estimates and detail on the sample size and confidence intervals is available online: &lt;a href = 'https://view.officeapps.live.com/op/view.aspx?src=https%3A%2F%2Fwww.health-ni.gov.uk%2Fsites%2Fdefault%2Ffiles%2F2026-05%2Fghq12-pfg-tables-hsni.xlsx&amp;wdOrigin=BROWSELINK' target = '_blank'&gt;from this link. &lt;/a&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2016-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The preventable mortality rate increased by 8 deaths per 100,000 population from 173 deaths per 100,000 population in 2016-20 to 181 deaths per 100,000 population in 2020-24. The change was statistically significant.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The comparison year has been set to 2021/22 due to changes in the data collection method as a result of Covid-19. While comparisons can be made between 2021/22 and 2024/25, it is important to note that participation in sport and physical activity in 2021/22 would have been impacted by closures due to Covid-19. Between 2021/22 and 2024/25 there have been consistent gaps in participation in sports and physical activity between adults with a disability compared with those without, adults with dependants compared with those without and for people living in the least and most deprived areas.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The comparison year has been set to 2022/23 due to changes in the data collection method as a result of, and closures due to, Covid-19. While comparisons can be made between 2021/22 and 2024/25, it is important to note that engaging in arts/cultural activities in 2021/22 would have been impacted by closures due to Covid-19, hence a comparison year of 2022/23 has been selected. There have been consistent gaps between males and females, people with a disability compared with those without, people with dependants compared with those without and between adults living in the most and least deprived areas.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">There has been a statistically significant change in the proportion of survey eligible businesses that sell outside Northern Ireland.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The percentage of good jobs in Northern Ireland has increased from 66.9% in 2021 to 69.0% in 2025.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Economic activity has increased gradually in recent years. Economic activity post-pandemic has recovered substantially and the latest 2025 data is now at a series high. Over the fourth quarter of 2025, economic output in Northern Ireland increased by 0.2%,  mainly driven by increased activity in the Construction sector. Quarterly figures are available: &lt;a href = 'https://www.nisra.gov.uk/statistics/economic-output-statistics/ni-composite-economic-index' target = '_blank'&gt;from this link. &lt;/a&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">However, trust in the media was lower in 2025 than in 2022 and 2023. It was similar to 2024.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">However, trust in the NI Assembly was higher in 2025 than in 2022 and 2023. It was similar to 2024.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
+    <numFmt numFmtId="165" formatCode="mm/dd/yyyy"/>
     <numFmt numFmtId="166" formatCode="dd/mm/yyyy"/>
   </numFmts>
   <fonts count="2">
@@ -651,7 +712,7 @@
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -665,8 +726,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:J261" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:J261"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:J313" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:J313"/>
   <tableColumns count="10">
     <tableColumn id="1" name="date"/>
     <tableColumn id="2" name="domain"/>
@@ -9274,6 +9335,1666 @@
         <v>170</v>
       </c>
     </row>
+    <row r="262">
+      <c r="A262" s="2" t="n">
+        <v>46197</v>
+      </c>
+      <c r="B262" t="s">
+        <v>10</v>
+      </c>
+      <c r="C262" t="s">
+        <v>11</v>
+      </c>
+      <c r="D262" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E262" s="3" t="n">
+        <v>63</v>
+      </c>
+      <c r="F262" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G262" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H262" s="3" t="n">
+        <v>68</v>
+      </c>
+      <c r="I262" t="s">
+        <v>15</v>
+      </c>
+      <c r="J262" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="2" t="n">
+        <v>46197</v>
+      </c>
+      <c r="B263" t="s">
+        <v>10</v>
+      </c>
+      <c r="C263" t="s">
+        <v>17</v>
+      </c>
+      <c r="D263" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E263" s="3" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="F263" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G263" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H263" s="3" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="I263" t="s">
+        <v>21</v>
+      </c>
+      <c r="J263" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="2" t="n">
+        <v>46197</v>
+      </c>
+      <c r="B264" t="s">
+        <v>10</v>
+      </c>
+      <c r="C264" t="s">
+        <v>23</v>
+      </c>
+      <c r="D264" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E264" s="3" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="F264" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G264" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H264" s="3" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="I264" t="s">
+        <v>21</v>
+      </c>
+      <c r="J264" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="2" t="n">
+        <v>46197</v>
+      </c>
+      <c r="B265" t="s">
+        <v>10</v>
+      </c>
+      <c r="C265" t="s">
+        <v>26</v>
+      </c>
+      <c r="D265" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E265" s="3" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="F265" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G265" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H265" s="3" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="I265" t="s">
+        <v>30</v>
+      </c>
+      <c r="J265" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="2" t="n">
+        <v>46197</v>
+      </c>
+      <c r="B266" t="s">
+        <v>32</v>
+      </c>
+      <c r="C266" t="s">
+        <v>33</v>
+      </c>
+      <c r="D266" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E266" s="3" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="F266" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G266" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H266" s="3" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="I266" t="s">
+        <v>15</v>
+      </c>
+      <c r="J266" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="2" t="n">
+        <v>46197</v>
+      </c>
+      <c r="B267" t="s">
+        <v>32</v>
+      </c>
+      <c r="C267" t="s">
+        <v>37</v>
+      </c>
+      <c r="D267" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E267" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="F267" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G267" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H267" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="I267" t="s">
+        <v>21</v>
+      </c>
+      <c r="J267" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="2" t="n">
+        <v>46197</v>
+      </c>
+      <c r="B268" t="s">
+        <v>32</v>
+      </c>
+      <c r="C268" t="s">
+        <v>39</v>
+      </c>
+      <c r="D268" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E268" s="3" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="F268" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="G268" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="H268" s="3" t="n">
+        <v>52</v>
+      </c>
+      <c r="I268" t="s">
+        <v>21</v>
+      </c>
+      <c r="J268" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="2" t="n">
+        <v>46197</v>
+      </c>
+      <c r="B269" t="s">
+        <v>32</v>
+      </c>
+      <c r="C269" t="s">
+        <v>44</v>
+      </c>
+      <c r="D269" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E269" s="3" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="F269" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G269" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H269" s="3" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="I269" t="s">
+        <v>15</v>
+      </c>
+      <c r="J269" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="2" t="n">
+        <v>46197</v>
+      </c>
+      <c r="B270" t="s">
+        <v>32</v>
+      </c>
+      <c r="C270" t="s">
+        <v>47</v>
+      </c>
+      <c r="D270" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E270" s="3" t="n">
+        <v>48.2</v>
+      </c>
+      <c r="F270" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G270" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="H270" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="I270" t="s">
+        <v>21</v>
+      </c>
+      <c r="J270" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="2" t="n">
+        <v>46197</v>
+      </c>
+      <c r="B271" t="s">
+        <v>32</v>
+      </c>
+      <c r="C271" t="s">
+        <v>50</v>
+      </c>
+      <c r="D271" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E271" s="3" t="n">
+        <v>51.9</v>
+      </c>
+      <c r="F271" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="G271" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H271" s="3" t="n">
+        <v>51</v>
+      </c>
+      <c r="I271" t="s">
+        <v>30</v>
+      </c>
+      <c r="J271" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="2" t="n">
+        <v>46197</v>
+      </c>
+      <c r="B272" t="s">
+        <v>32</v>
+      </c>
+      <c r="C272" t="s">
+        <v>53</v>
+      </c>
+      <c r="D272" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="E272" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="F272" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="G272" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H272" s="3" t="n">
+        <v>47</v>
+      </c>
+      <c r="I272" t="s">
+        <v>15</v>
+      </c>
+      <c r="J272" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="2" t="n">
+        <v>46197</v>
+      </c>
+      <c r="B273" t="s">
+        <v>32</v>
+      </c>
+      <c r="C273" t="s">
+        <v>56</v>
+      </c>
+      <c r="D273" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E273" s="3" t="n">
+        <v>0.063</v>
+      </c>
+      <c r="F273" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="G273" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H273" s="3" t="n">
+        <v>0.07</v>
+      </c>
+      <c r="I273" t="s">
+        <v>30</v>
+      </c>
+      <c r="J273" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="2" t="n">
+        <v>46197</v>
+      </c>
+      <c r="B274" t="s">
+        <v>32</v>
+      </c>
+      <c r="C274" t="s">
+        <v>59</v>
+      </c>
+      <c r="D274" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E274" s="3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="F274" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="G274" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H274" s="3" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="I274" t="s">
+        <v>30</v>
+      </c>
+      <c r="J274" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="2" t="n">
+        <v>46197</v>
+      </c>
+      <c r="B275" t="s">
+        <v>63</v>
+      </c>
+      <c r="C275" t="s">
+        <v>64</v>
+      </c>
+      <c r="D275" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E275" s="3" t="n">
+        <v>49.6</v>
+      </c>
+      <c r="F275" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="G275" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H275" s="3" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="I275" t="s">
+        <v>15</v>
+      </c>
+      <c r="J275" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="2" t="n">
+        <v>46197</v>
+      </c>
+      <c r="B276" t="s">
+        <v>63</v>
+      </c>
+      <c r="C276" t="s">
+        <v>67</v>
+      </c>
+      <c r="D276" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E276" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="F276" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="G276" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="H276" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="I276" t="s">
+        <v>30</v>
+      </c>
+      <c r="J276" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="2" t="n">
+        <v>46197</v>
+      </c>
+      <c r="B277" t="s">
+        <v>63</v>
+      </c>
+      <c r="C277" t="s">
+        <v>71</v>
+      </c>
+      <c r="D277" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E277" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="F277" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="G277" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="H277" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="I277" t="s">
+        <v>30</v>
+      </c>
+      <c r="J277" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="2" t="n">
+        <v>46197</v>
+      </c>
+      <c r="B278" t="s">
+        <v>63</v>
+      </c>
+      <c r="C278" t="s">
+        <v>73</v>
+      </c>
+      <c r="D278" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E278" s="3" t="n">
+        <v>36.1</v>
+      </c>
+      <c r="F278" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="G278" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H278" s="3" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="I278" t="s">
+        <v>21</v>
+      </c>
+      <c r="J278" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="2" t="n">
+        <v>46197</v>
+      </c>
+      <c r="B279" t="s">
+        <v>75</v>
+      </c>
+      <c r="C279" t="s">
+        <v>76</v>
+      </c>
+      <c r="D279" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E279" s="3" t="n">
+        <v>56</v>
+      </c>
+      <c r="F279" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="G279" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H279" s="3" t="n">
+        <v>56.3</v>
+      </c>
+      <c r="I279" t="s">
+        <v>30</v>
+      </c>
+      <c r="J279" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="2" t="n">
+        <v>46197</v>
+      </c>
+      <c r="B280" t="s">
+        <v>75</v>
+      </c>
+      <c r="C280" t="s">
+        <v>78</v>
+      </c>
+      <c r="D280" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="E280" s="3" t="n">
+        <v>62.1</v>
+      </c>
+      <c r="F280" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="G280" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="H280" s="3" t="n">
+        <v>60.2</v>
+      </c>
+      <c r="I280" t="s">
+        <v>21</v>
+      </c>
+      <c r="J280" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="2" t="n">
+        <v>46197</v>
+      </c>
+      <c r="B281" t="s">
+        <v>75</v>
+      </c>
+      <c r="C281" t="s">
+        <v>83</v>
+      </c>
+      <c r="D281" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="E281" s="3" t="n">
+        <v>60.1</v>
+      </c>
+      <c r="F281" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="G281" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="H281" s="3" t="n">
+        <v>59.3</v>
+      </c>
+      <c r="I281" t="s">
+        <v>30</v>
+      </c>
+      <c r="J281" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="2" t="n">
+        <v>46197</v>
+      </c>
+      <c r="B282" t="s">
+        <v>75</v>
+      </c>
+      <c r="C282" t="s">
+        <v>86</v>
+      </c>
+      <c r="D282" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E282" s="3" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="F282" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="G282" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H282" s="3" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="I282" t="s">
+        <v>15</v>
+      </c>
+      <c r="J282" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="2" t="n">
+        <v>46197</v>
+      </c>
+      <c r="B283" t="s">
+        <v>75</v>
+      </c>
+      <c r="C283" t="s">
+        <v>89</v>
+      </c>
+      <c r="D283" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="E283" s="3" t="n">
+        <v>173</v>
+      </c>
+      <c r="F283" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="G283" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="H283" s="3" t="n">
+        <v>181</v>
+      </c>
+      <c r="I283" t="s">
+        <v>21</v>
+      </c>
+      <c r="J283" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="2" t="n">
+        <v>46197</v>
+      </c>
+      <c r="B284" t="s">
+        <v>75</v>
+      </c>
+      <c r="C284" t="s">
+        <v>94</v>
+      </c>
+      <c r="D284" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E284" s="3" t="n">
+        <v>75</v>
+      </c>
+      <c r="F284" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="G284" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H284" s="3" t="n">
+        <v>73</v>
+      </c>
+      <c r="I284" t="s">
+        <v>21</v>
+      </c>
+      <c r="J284" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="2" t="n">
+        <v>46197</v>
+      </c>
+      <c r="B285" t="s">
+        <v>98</v>
+      </c>
+      <c r="C285" t="s">
+        <v>99</v>
+      </c>
+      <c r="D285" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E285" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="F285" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="G285" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H285" s="3" t="n">
+        <v>85</v>
+      </c>
+      <c r="I285" t="s">
+        <v>15</v>
+      </c>
+      <c r="J285" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="2" t="n">
+        <v>46197</v>
+      </c>
+      <c r="B286" t="s">
+        <v>98</v>
+      </c>
+      <c r="C286" t="s">
+        <v>101</v>
+      </c>
+      <c r="D286" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E286" s="3" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="F286" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="G286" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H286" s="3" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="I286" t="s">
+        <v>30</v>
+      </c>
+      <c r="J286" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="2" t="n">
+        <v>46197</v>
+      </c>
+      <c r="B287" t="s">
+        <v>98</v>
+      </c>
+      <c r="C287" t="s">
+        <v>104</v>
+      </c>
+      <c r="D287" s="3"/>
+      <c r="E287" s="3"/>
+      <c r="F287" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="G287" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="H287" s="3" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="I287" t="s">
+        <v>61</v>
+      </c>
+      <c r="J287" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="2" t="n">
+        <v>46197</v>
+      </c>
+      <c r="B288" t="s">
+        <v>98</v>
+      </c>
+      <c r="C288" t="s">
+        <v>106</v>
+      </c>
+      <c r="D288" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E288" s="3" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="F288" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="G288" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H288" s="3" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="I288" t="s">
+        <v>21</v>
+      </c>
+      <c r="J288" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="2" t="n">
+        <v>46197</v>
+      </c>
+      <c r="B289" t="s">
+        <v>108</v>
+      </c>
+      <c r="C289" t="s">
+        <v>109</v>
+      </c>
+      <c r="D289" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E289" s="3" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="F289" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="G289" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H289" s="3" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="I289" t="s">
+        <v>15</v>
+      </c>
+      <c r="J289" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="2" t="n">
+        <v>46197</v>
+      </c>
+      <c r="B290" t="s">
+        <v>108</v>
+      </c>
+      <c r="C290" t="s">
+        <v>111</v>
+      </c>
+      <c r="D290" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E290" s="3" t="n">
+        <v>69.8</v>
+      </c>
+      <c r="F290" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="G290" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H290" s="3" t="n">
+        <v>74.3</v>
+      </c>
+      <c r="I290" t="s">
+        <v>15</v>
+      </c>
+      <c r="J290" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="2" t="n">
+        <v>46197</v>
+      </c>
+      <c r="B291" t="s">
+        <v>108</v>
+      </c>
+      <c r="C291" t="s">
+        <v>114</v>
+      </c>
+      <c r="D291" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E291" s="3" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="F291" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="G291" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H291" s="3" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="I291" t="s">
+        <v>15</v>
+      </c>
+      <c r="J291" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="2" t="n">
+        <v>46197</v>
+      </c>
+      <c r="B292" t="s">
+        <v>108</v>
+      </c>
+      <c r="C292" t="s">
+        <v>117</v>
+      </c>
+      <c r="D292" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="E292" s="3" t="n">
+        <v>66.9</v>
+      </c>
+      <c r="F292" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="G292" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H292" s="3" t="n">
+        <v>69</v>
+      </c>
+      <c r="I292" t="s">
+        <v>15</v>
+      </c>
+      <c r="J292" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="2" t="n">
+        <v>46197</v>
+      </c>
+      <c r="B293" t="s">
+        <v>108</v>
+      </c>
+      <c r="C293" t="s">
+        <v>119</v>
+      </c>
+      <c r="D293" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="E293" s="3" t="n">
+        <v>61.27</v>
+      </c>
+      <c r="F293" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G293" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H293" s="3" t="n">
+        <v>62.21</v>
+      </c>
+      <c r="I293" t="s">
+        <v>30</v>
+      </c>
+      <c r="J293" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="2" t="n">
+        <v>46197</v>
+      </c>
+      <c r="B294" t="s">
+        <v>108</v>
+      </c>
+      <c r="C294" t="s">
+        <v>121</v>
+      </c>
+      <c r="D294" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E294" s="3" t="n">
+        <v>92.8</v>
+      </c>
+      <c r="F294" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G294" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H294" s="3" t="n">
+        <v>99.5</v>
+      </c>
+      <c r="I294" t="s">
+        <v>15</v>
+      </c>
+      <c r="J294" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="2" t="n">
+        <v>46197</v>
+      </c>
+      <c r="B295" t="s">
+        <v>108</v>
+      </c>
+      <c r="C295" t="s">
+        <v>123</v>
+      </c>
+      <c r="D295" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="E295" s="3" t="n">
+        <v>96.3</v>
+      </c>
+      <c r="F295" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G295" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H295" s="3" t="n">
+        <v>104.4</v>
+      </c>
+      <c r="I295" t="s">
+        <v>15</v>
+      </c>
+      <c r="J295" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="2" t="n">
+        <v>46197</v>
+      </c>
+      <c r="B296" t="s">
+        <v>108</v>
+      </c>
+      <c r="C296" t="s">
+        <v>126</v>
+      </c>
+      <c r="D296" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E296" s="3" t="n">
+        <v>1170.4</v>
+      </c>
+      <c r="F296" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G296" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H296" s="3" t="n">
+        <v>1000.7</v>
+      </c>
+      <c r="I296" t="s">
+        <v>21</v>
+      </c>
+      <c r="J296" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="2" t="n">
+        <v>46197</v>
+      </c>
+      <c r="B297" t="s">
+        <v>108</v>
+      </c>
+      <c r="C297" t="s">
+        <v>128</v>
+      </c>
+      <c r="D297" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E297" s="3" t="n">
+        <v>76.3</v>
+      </c>
+      <c r="F297" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="G297" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H297" s="3" t="n">
+        <v>80.4</v>
+      </c>
+      <c r="I297" t="s">
+        <v>15</v>
+      </c>
+      <c r="J297" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="2" t="n">
+        <v>46197</v>
+      </c>
+      <c r="B298" t="s">
+        <v>131</v>
+      </c>
+      <c r="C298" t="s">
+        <v>132</v>
+      </c>
+      <c r="D298" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E298" s="3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="F298" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="G298" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="H298" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I298" t="s">
+        <v>30</v>
+      </c>
+      <c r="J298" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="2" t="n">
+        <v>46197</v>
+      </c>
+      <c r="B299" t="s">
+        <v>131</v>
+      </c>
+      <c r="C299" t="s">
+        <v>134</v>
+      </c>
+      <c r="D299" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E299" s="3" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="F299" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="G299" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="H299" s="3" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="I299" t="s">
+        <v>30</v>
+      </c>
+      <c r="J299" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="2" t="n">
+        <v>46197</v>
+      </c>
+      <c r="B300" t="s">
+        <v>131</v>
+      </c>
+      <c r="C300" t="s">
+        <v>136</v>
+      </c>
+      <c r="D300" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="E300" s="3" t="n">
+        <v>193</v>
+      </c>
+      <c r="F300" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="G300" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H300" s="3" t="n">
+        <v>189</v>
+      </c>
+      <c r="I300" t="s">
+        <v>30</v>
+      </c>
+      <c r="J300" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="2" t="n">
+        <v>46197</v>
+      </c>
+      <c r="B301" t="s">
+        <v>131</v>
+      </c>
+      <c r="C301" t="s">
+        <v>140</v>
+      </c>
+      <c r="D301" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E301" s="3" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="F301" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="G301" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H301" s="3" t="n">
+        <v>40.7</v>
+      </c>
+      <c r="I301" t="s">
+        <v>21</v>
+      </c>
+      <c r="J301" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="2" t="n">
+        <v>46197</v>
+      </c>
+      <c r="B302" t="s">
+        <v>131</v>
+      </c>
+      <c r="C302" t="s">
+        <v>142</v>
+      </c>
+      <c r="D302" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E302" s="3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="F302" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="G302" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="H302" s="3" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="I302" t="s">
+        <v>30</v>
+      </c>
+      <c r="J302" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="2" t="n">
+        <v>46197</v>
+      </c>
+      <c r="B303" t="s">
+        <v>145</v>
+      </c>
+      <c r="C303" t="s">
+        <v>146</v>
+      </c>
+      <c r="D303" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E303" s="3" t="n">
+        <v>68.4</v>
+      </c>
+      <c r="F303" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G303" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H303" s="3" t="n">
+        <v>69.2</v>
+      </c>
+      <c r="I303" t="s">
+        <v>30</v>
+      </c>
+      <c r="J303" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="2" t="n">
+        <v>46197</v>
+      </c>
+      <c r="B304" t="s">
+        <v>145</v>
+      </c>
+      <c r="C304" t="s">
+        <v>148</v>
+      </c>
+      <c r="D304" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E304" s="3" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="F304" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="G304" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H304" s="3" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="I304" t="s">
+        <v>15</v>
+      </c>
+      <c r="J304" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="2" t="n">
+        <v>46197</v>
+      </c>
+      <c r="B305" t="s">
+        <v>145</v>
+      </c>
+      <c r="C305" t="s">
+        <v>150</v>
+      </c>
+      <c r="D305" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="E305" s="3" t="n">
+        <v>47</v>
+      </c>
+      <c r="F305" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="G305" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H305" s="3" t="n">
+        <v>46</v>
+      </c>
+      <c r="I305" t="s">
+        <v>30</v>
+      </c>
+      <c r="J305" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="2" t="n">
+        <v>46197</v>
+      </c>
+      <c r="B306" t="s">
+        <v>152</v>
+      </c>
+      <c r="C306" t="s">
+        <v>153</v>
+      </c>
+      <c r="D306" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E306" s="3" t="n">
+        <v>90</v>
+      </c>
+      <c r="F306" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="G306" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H306" s="3" t="n">
+        <v>91</v>
+      </c>
+      <c r="I306" t="s">
+        <v>30</v>
+      </c>
+      <c r="J306" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="2" t="n">
+        <v>46197</v>
+      </c>
+      <c r="B307" t="s">
+        <v>152</v>
+      </c>
+      <c r="C307" t="s">
+        <v>154</v>
+      </c>
+      <c r="D307" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E307" s="3" t="n">
+        <v>10135</v>
+      </c>
+      <c r="F307" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="G307" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H307" s="3" t="n">
+        <v>10855</v>
+      </c>
+      <c r="I307" t="s">
+        <v>21</v>
+      </c>
+      <c r="J307" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="2" t="n">
+        <v>46197</v>
+      </c>
+      <c r="B308" t="s">
+        <v>152</v>
+      </c>
+      <c r="C308" t="s">
+        <v>156</v>
+      </c>
+      <c r="D308" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E308" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F308" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="G308" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="H308" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="I308" t="s">
+        <v>30</v>
+      </c>
+      <c r="J308" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="2" t="n">
+        <v>46197</v>
+      </c>
+      <c r="B309" t="s">
+        <v>152</v>
+      </c>
+      <c r="C309" t="s">
+        <v>159</v>
+      </c>
+      <c r="D309" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="E309" s="3" t="n">
+        <v>30288</v>
+      </c>
+      <c r="F309" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="G309" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H309" s="3" t="n">
+        <v>37635</v>
+      </c>
+      <c r="I309" t="s">
+        <v>21</v>
+      </c>
+      <c r="J309" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="2" t="n">
+        <v>46197</v>
+      </c>
+      <c r="B310" t="s">
+        <v>161</v>
+      </c>
+      <c r="C310" t="s">
+        <v>162</v>
+      </c>
+      <c r="D310" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E310" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="F310" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="G310" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H310" s="3" t="n">
+        <v>46.7</v>
+      </c>
+      <c r="I310" t="s">
+        <v>15</v>
+      </c>
+      <c r="J310" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="2" t="n">
+        <v>46197</v>
+      </c>
+      <c r="B311" t="s">
+        <v>161</v>
+      </c>
+      <c r="C311" t="s">
+        <v>164</v>
+      </c>
+      <c r="D311" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E311" s="3" t="n">
+        <v>78.6</v>
+      </c>
+      <c r="F311" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="G311" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H311" s="3" t="n">
+        <v>76.1</v>
+      </c>
+      <c r="I311" t="s">
+        <v>21</v>
+      </c>
+      <c r="J311" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="2" t="n">
+        <v>46197</v>
+      </c>
+      <c r="B312" t="s">
+        <v>161</v>
+      </c>
+      <c r="C312" t="s">
+        <v>165</v>
+      </c>
+      <c r="D312" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="E312" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="F312" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="G312" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H312" s="3" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="I312" t="s">
+        <v>30</v>
+      </c>
+      <c r="J312" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="2" t="n">
+        <v>46197</v>
+      </c>
+      <c r="B313" t="s">
+        <v>161</v>
+      </c>
+      <c r="C313" t="s">
+        <v>168</v>
+      </c>
+      <c r="D313" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="E313" s="3" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="F313" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="G313" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H313" s="3" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="I313" t="s">
+        <v>30</v>
+      </c>
+      <c r="J313" t="s">
+        <v>217</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/indicator-performance-table.xlsx
+++ b/indicator-performance-table.xlsx
@@ -672,8 +672,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
-    <numFmt numFmtId="165" formatCode="mm/dd/yyyy"/>
+  <numFmts count="1">
     <numFmt numFmtId="166" formatCode="dd/mm/yyyy"/>
   </numFmts>
   <fonts count="2">
@@ -712,7 +711,7 @@
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -726,8 +725,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:J313" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:J313"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:J365" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:J365"/>
   <tableColumns count="10">
     <tableColumn id="1" name="date"/>
     <tableColumn id="2" name="domain"/>
@@ -10995,6 +10994,1666 @@
         <v>217</v>
       </c>
     </row>
+    <row r="314">
+      <c r="A314" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B314" t="s">
+        <v>10</v>
+      </c>
+      <c r="C314" t="s">
+        <v>11</v>
+      </c>
+      <c r="D314" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E314" s="3" t="n">
+        <v>63</v>
+      </c>
+      <c r="F314" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G314" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H314" s="3" t="n">
+        <v>68</v>
+      </c>
+      <c r="I314" t="s">
+        <v>15</v>
+      </c>
+      <c r="J314" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B315" t="s">
+        <v>10</v>
+      </c>
+      <c r="C315" t="s">
+        <v>17</v>
+      </c>
+      <c r="D315" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E315" s="3" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="F315" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G315" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H315" s="3" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="I315" t="s">
+        <v>21</v>
+      </c>
+      <c r="J315" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B316" t="s">
+        <v>10</v>
+      </c>
+      <c r="C316" t="s">
+        <v>23</v>
+      </c>
+      <c r="D316" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E316" s="3" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="F316" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G316" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H316" s="3" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="I316" t="s">
+        <v>21</v>
+      </c>
+      <c r="J316" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B317" t="s">
+        <v>10</v>
+      </c>
+      <c r="C317" t="s">
+        <v>26</v>
+      </c>
+      <c r="D317" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E317" s="3" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="F317" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G317" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H317" s="3" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="I317" t="s">
+        <v>30</v>
+      </c>
+      <c r="J317" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B318" t="s">
+        <v>32</v>
+      </c>
+      <c r="C318" t="s">
+        <v>33</v>
+      </c>
+      <c r="D318" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E318" s="3" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="F318" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G318" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H318" s="3" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="I318" t="s">
+        <v>15</v>
+      </c>
+      <c r="J318" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B319" t="s">
+        <v>32</v>
+      </c>
+      <c r="C319" t="s">
+        <v>37</v>
+      </c>
+      <c r="D319" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E319" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="F319" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G319" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H319" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="I319" t="s">
+        <v>21</v>
+      </c>
+      <c r="J319" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B320" t="s">
+        <v>32</v>
+      </c>
+      <c r="C320" t="s">
+        <v>39</v>
+      </c>
+      <c r="D320" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E320" s="3" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="F320" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="G320" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="H320" s="3" t="n">
+        <v>52</v>
+      </c>
+      <c r="I320" t="s">
+        <v>21</v>
+      </c>
+      <c r="J320" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B321" t="s">
+        <v>32</v>
+      </c>
+      <c r="C321" t="s">
+        <v>44</v>
+      </c>
+      <c r="D321" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E321" s="3" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="F321" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G321" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H321" s="3" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="I321" t="s">
+        <v>15</v>
+      </c>
+      <c r="J321" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B322" t="s">
+        <v>32</v>
+      </c>
+      <c r="C322" t="s">
+        <v>47</v>
+      </c>
+      <c r="D322" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E322" s="3" t="n">
+        <v>48.2</v>
+      </c>
+      <c r="F322" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G322" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="H322" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="I322" t="s">
+        <v>21</v>
+      </c>
+      <c r="J322" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B323" t="s">
+        <v>32</v>
+      </c>
+      <c r="C323" t="s">
+        <v>50</v>
+      </c>
+      <c r="D323" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E323" s="3" t="n">
+        <v>51.9</v>
+      </c>
+      <c r="F323" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="G323" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H323" s="3" t="n">
+        <v>51</v>
+      </c>
+      <c r="I323" t="s">
+        <v>30</v>
+      </c>
+      <c r="J323" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B324" t="s">
+        <v>32</v>
+      </c>
+      <c r="C324" t="s">
+        <v>53</v>
+      </c>
+      <c r="D324" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="E324" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="F324" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="G324" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H324" s="3" t="n">
+        <v>47</v>
+      </c>
+      <c r="I324" t="s">
+        <v>15</v>
+      </c>
+      <c r="J324" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B325" t="s">
+        <v>32</v>
+      </c>
+      <c r="C325" t="s">
+        <v>56</v>
+      </c>
+      <c r="D325" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E325" s="3" t="n">
+        <v>0.063</v>
+      </c>
+      <c r="F325" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="G325" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H325" s="3" t="n">
+        <v>0.07</v>
+      </c>
+      <c r="I325" t="s">
+        <v>30</v>
+      </c>
+      <c r="J325" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B326" t="s">
+        <v>32</v>
+      </c>
+      <c r="C326" t="s">
+        <v>59</v>
+      </c>
+      <c r="D326" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E326" s="3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="F326" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="G326" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H326" s="3" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="I326" t="s">
+        <v>30</v>
+      </c>
+      <c r="J326" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B327" t="s">
+        <v>63</v>
+      </c>
+      <c r="C327" t="s">
+        <v>64</v>
+      </c>
+      <c r="D327" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E327" s="3" t="n">
+        <v>49.6</v>
+      </c>
+      <c r="F327" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="G327" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H327" s="3" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="I327" t="s">
+        <v>15</v>
+      </c>
+      <c r="J327" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B328" t="s">
+        <v>63</v>
+      </c>
+      <c r="C328" t="s">
+        <v>67</v>
+      </c>
+      <c r="D328" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E328" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="F328" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="G328" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="H328" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="I328" t="s">
+        <v>30</v>
+      </c>
+      <c r="J328" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B329" t="s">
+        <v>63</v>
+      </c>
+      <c r="C329" t="s">
+        <v>71</v>
+      </c>
+      <c r="D329" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E329" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="F329" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="G329" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="H329" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="I329" t="s">
+        <v>30</v>
+      </c>
+      <c r="J329" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B330" t="s">
+        <v>63</v>
+      </c>
+      <c r="C330" t="s">
+        <v>73</v>
+      </c>
+      <c r="D330" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E330" s="3" t="n">
+        <v>36.1</v>
+      </c>
+      <c r="F330" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="G330" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H330" s="3" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="I330" t="s">
+        <v>21</v>
+      </c>
+      <c r="J330" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B331" t="s">
+        <v>75</v>
+      </c>
+      <c r="C331" t="s">
+        <v>76</v>
+      </c>
+      <c r="D331" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E331" s="3" t="n">
+        <v>56</v>
+      </c>
+      <c r="F331" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="G331" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H331" s="3" t="n">
+        <v>56.3</v>
+      </c>
+      <c r="I331" t="s">
+        <v>30</v>
+      </c>
+      <c r="J331" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B332" t="s">
+        <v>75</v>
+      </c>
+      <c r="C332" t="s">
+        <v>78</v>
+      </c>
+      <c r="D332" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="E332" s="3" t="n">
+        <v>62.1</v>
+      </c>
+      <c r="F332" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="G332" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="H332" s="3" t="n">
+        <v>60.2</v>
+      </c>
+      <c r="I332" t="s">
+        <v>21</v>
+      </c>
+      <c r="J332" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B333" t="s">
+        <v>75</v>
+      </c>
+      <c r="C333" t="s">
+        <v>83</v>
+      </c>
+      <c r="D333" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="E333" s="3" t="n">
+        <v>60.1</v>
+      </c>
+      <c r="F333" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="G333" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="H333" s="3" t="n">
+        <v>59.3</v>
+      </c>
+      <c r="I333" t="s">
+        <v>30</v>
+      </c>
+      <c r="J333" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B334" t="s">
+        <v>75</v>
+      </c>
+      <c r="C334" t="s">
+        <v>86</v>
+      </c>
+      <c r="D334" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E334" s="3" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="F334" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="G334" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H334" s="3" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="I334" t="s">
+        <v>15</v>
+      </c>
+      <c r="J334" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B335" t="s">
+        <v>75</v>
+      </c>
+      <c r="C335" t="s">
+        <v>89</v>
+      </c>
+      <c r="D335" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="E335" s="3" t="n">
+        <v>173</v>
+      </c>
+      <c r="F335" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="G335" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="H335" s="3" t="n">
+        <v>181</v>
+      </c>
+      <c r="I335" t="s">
+        <v>21</v>
+      </c>
+      <c r="J335" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B336" t="s">
+        <v>75</v>
+      </c>
+      <c r="C336" t="s">
+        <v>94</v>
+      </c>
+      <c r="D336" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E336" s="3" t="n">
+        <v>75</v>
+      </c>
+      <c r="F336" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="G336" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H336" s="3" t="n">
+        <v>73</v>
+      </c>
+      <c r="I336" t="s">
+        <v>21</v>
+      </c>
+      <c r="J336" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B337" t="s">
+        <v>98</v>
+      </c>
+      <c r="C337" t="s">
+        <v>99</v>
+      </c>
+      <c r="D337" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E337" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="F337" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="G337" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H337" s="3" t="n">
+        <v>85</v>
+      </c>
+      <c r="I337" t="s">
+        <v>15</v>
+      </c>
+      <c r="J337" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B338" t="s">
+        <v>98</v>
+      </c>
+      <c r="C338" t="s">
+        <v>101</v>
+      </c>
+      <c r="D338" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E338" s="3" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="F338" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="G338" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H338" s="3" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="I338" t="s">
+        <v>30</v>
+      </c>
+      <c r="J338" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B339" t="s">
+        <v>98</v>
+      </c>
+      <c r="C339" t="s">
+        <v>104</v>
+      </c>
+      <c r="D339" s="3"/>
+      <c r="E339" s="3"/>
+      <c r="F339" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="G339" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="H339" s="3" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="I339" t="s">
+        <v>61</v>
+      </c>
+      <c r="J339" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B340" t="s">
+        <v>98</v>
+      </c>
+      <c r="C340" t="s">
+        <v>106</v>
+      </c>
+      <c r="D340" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E340" s="3" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="F340" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="G340" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H340" s="3" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="I340" t="s">
+        <v>21</v>
+      </c>
+      <c r="J340" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B341" t="s">
+        <v>108</v>
+      </c>
+      <c r="C341" t="s">
+        <v>109</v>
+      </c>
+      <c r="D341" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E341" s="3" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="F341" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="G341" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H341" s="3" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="I341" t="s">
+        <v>15</v>
+      </c>
+      <c r="J341" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B342" t="s">
+        <v>108</v>
+      </c>
+      <c r="C342" t="s">
+        <v>111</v>
+      </c>
+      <c r="D342" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E342" s="3" t="n">
+        <v>69.8</v>
+      </c>
+      <c r="F342" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="G342" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H342" s="3" t="n">
+        <v>74.3</v>
+      </c>
+      <c r="I342" t="s">
+        <v>15</v>
+      </c>
+      <c r="J342" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B343" t="s">
+        <v>108</v>
+      </c>
+      <c r="C343" t="s">
+        <v>114</v>
+      </c>
+      <c r="D343" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E343" s="3" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="F343" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="G343" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H343" s="3" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="I343" t="s">
+        <v>15</v>
+      </c>
+      <c r="J343" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B344" t="s">
+        <v>108</v>
+      </c>
+      <c r="C344" t="s">
+        <v>117</v>
+      </c>
+      <c r="D344" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="E344" s="3" t="n">
+        <v>66.9</v>
+      </c>
+      <c r="F344" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="G344" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H344" s="3" t="n">
+        <v>69</v>
+      </c>
+      <c r="I344" t="s">
+        <v>15</v>
+      </c>
+      <c r="J344" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B345" t="s">
+        <v>108</v>
+      </c>
+      <c r="C345" t="s">
+        <v>119</v>
+      </c>
+      <c r="D345" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="E345" s="3" t="n">
+        <v>61.27</v>
+      </c>
+      <c r="F345" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G345" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H345" s="3" t="n">
+        <v>62.21</v>
+      </c>
+      <c r="I345" t="s">
+        <v>30</v>
+      </c>
+      <c r="J345" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B346" t="s">
+        <v>108</v>
+      </c>
+      <c r="C346" t="s">
+        <v>121</v>
+      </c>
+      <c r="D346" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E346" s="3" t="n">
+        <v>92.8</v>
+      </c>
+      <c r="F346" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G346" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H346" s="3" t="n">
+        <v>99.5</v>
+      </c>
+      <c r="I346" t="s">
+        <v>15</v>
+      </c>
+      <c r="J346" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B347" t="s">
+        <v>108</v>
+      </c>
+      <c r="C347" t="s">
+        <v>123</v>
+      </c>
+      <c r="D347" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="E347" s="3" t="n">
+        <v>96.3</v>
+      </c>
+      <c r="F347" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G347" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H347" s="3" t="n">
+        <v>104.4</v>
+      </c>
+      <c r="I347" t="s">
+        <v>15</v>
+      </c>
+      <c r="J347" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B348" t="s">
+        <v>108</v>
+      </c>
+      <c r="C348" t="s">
+        <v>126</v>
+      </c>
+      <c r="D348" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E348" s="3" t="n">
+        <v>1170.4</v>
+      </c>
+      <c r="F348" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G348" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H348" s="3" t="n">
+        <v>1000.7</v>
+      </c>
+      <c r="I348" t="s">
+        <v>21</v>
+      </c>
+      <c r="J348" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B349" t="s">
+        <v>108</v>
+      </c>
+      <c r="C349" t="s">
+        <v>128</v>
+      </c>
+      <c r="D349" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E349" s="3" t="n">
+        <v>76.3</v>
+      </c>
+      <c r="F349" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="G349" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H349" s="3" t="n">
+        <v>80.4</v>
+      </c>
+      <c r="I349" t="s">
+        <v>15</v>
+      </c>
+      <c r="J349" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B350" t="s">
+        <v>131</v>
+      </c>
+      <c r="C350" t="s">
+        <v>132</v>
+      </c>
+      <c r="D350" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E350" s="3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="F350" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="G350" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="H350" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I350" t="s">
+        <v>30</v>
+      </c>
+      <c r="J350" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B351" t="s">
+        <v>131</v>
+      </c>
+      <c r="C351" t="s">
+        <v>134</v>
+      </c>
+      <c r="D351" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E351" s="3" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="F351" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="G351" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="H351" s="3" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="I351" t="s">
+        <v>30</v>
+      </c>
+      <c r="J351" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B352" t="s">
+        <v>131</v>
+      </c>
+      <c r="C352" t="s">
+        <v>136</v>
+      </c>
+      <c r="D352" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="E352" s="3" t="n">
+        <v>193</v>
+      </c>
+      <c r="F352" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="G352" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H352" s="3" t="n">
+        <v>189</v>
+      </c>
+      <c r="I352" t="s">
+        <v>30</v>
+      </c>
+      <c r="J352" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B353" t="s">
+        <v>131</v>
+      </c>
+      <c r="C353" t="s">
+        <v>140</v>
+      </c>
+      <c r="D353" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E353" s="3" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="F353" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="G353" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H353" s="3" t="n">
+        <v>40.7</v>
+      </c>
+      <c r="I353" t="s">
+        <v>21</v>
+      </c>
+      <c r="J353" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B354" t="s">
+        <v>131</v>
+      </c>
+      <c r="C354" t="s">
+        <v>142</v>
+      </c>
+      <c r="D354" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E354" s="3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="F354" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="G354" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="H354" s="3" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="I354" t="s">
+        <v>30</v>
+      </c>
+      <c r="J354" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B355" t="s">
+        <v>145</v>
+      </c>
+      <c r="C355" t="s">
+        <v>146</v>
+      </c>
+      <c r="D355" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E355" s="3" t="n">
+        <v>68.4</v>
+      </c>
+      <c r="F355" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G355" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H355" s="3" t="n">
+        <v>69.2</v>
+      </c>
+      <c r="I355" t="s">
+        <v>30</v>
+      </c>
+      <c r="J355" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B356" t="s">
+        <v>145</v>
+      </c>
+      <c r="C356" t="s">
+        <v>148</v>
+      </c>
+      <c r="D356" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E356" s="3" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="F356" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="G356" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H356" s="3" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="I356" t="s">
+        <v>15</v>
+      </c>
+      <c r="J356" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B357" t="s">
+        <v>145</v>
+      </c>
+      <c r="C357" t="s">
+        <v>150</v>
+      </c>
+      <c r="D357" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="E357" s="3" t="n">
+        <v>47</v>
+      </c>
+      <c r="F357" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="G357" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H357" s="3" t="n">
+        <v>46</v>
+      </c>
+      <c r="I357" t="s">
+        <v>30</v>
+      </c>
+      <c r="J357" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B358" t="s">
+        <v>152</v>
+      </c>
+      <c r="C358" t="s">
+        <v>153</v>
+      </c>
+      <c r="D358" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E358" s="3" t="n">
+        <v>90</v>
+      </c>
+      <c r="F358" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="G358" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H358" s="3" t="n">
+        <v>91</v>
+      </c>
+      <c r="I358" t="s">
+        <v>30</v>
+      </c>
+      <c r="J358" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B359" t="s">
+        <v>152</v>
+      </c>
+      <c r="C359" t="s">
+        <v>154</v>
+      </c>
+      <c r="D359" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E359" s="3" t="n">
+        <v>10135</v>
+      </c>
+      <c r="F359" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="G359" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H359" s="3" t="n">
+        <v>10855</v>
+      </c>
+      <c r="I359" t="s">
+        <v>21</v>
+      </c>
+      <c r="J359" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B360" t="s">
+        <v>152</v>
+      </c>
+      <c r="C360" t="s">
+        <v>156</v>
+      </c>
+      <c r="D360" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E360" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F360" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="G360" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="H360" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="I360" t="s">
+        <v>30</v>
+      </c>
+      <c r="J360" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B361" t="s">
+        <v>152</v>
+      </c>
+      <c r="C361" t="s">
+        <v>159</v>
+      </c>
+      <c r="D361" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="E361" s="3" t="n">
+        <v>30288</v>
+      </c>
+      <c r="F361" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="G361" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H361" s="3" t="n">
+        <v>37635</v>
+      </c>
+      <c r="I361" t="s">
+        <v>21</v>
+      </c>
+      <c r="J361" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B362" t="s">
+        <v>161</v>
+      </c>
+      <c r="C362" t="s">
+        <v>162</v>
+      </c>
+      <c r="D362" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E362" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="F362" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="G362" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H362" s="3" t="n">
+        <v>46.7</v>
+      </c>
+      <c r="I362" t="s">
+        <v>15</v>
+      </c>
+      <c r="J362" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B363" t="s">
+        <v>161</v>
+      </c>
+      <c r="C363" t="s">
+        <v>164</v>
+      </c>
+      <c r="D363" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E363" s="3" t="n">
+        <v>78.6</v>
+      </c>
+      <c r="F363" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="G363" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H363" s="3" t="n">
+        <v>76.1</v>
+      </c>
+      <c r="I363" t="s">
+        <v>21</v>
+      </c>
+      <c r="J363" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B364" t="s">
+        <v>161</v>
+      </c>
+      <c r="C364" t="s">
+        <v>165</v>
+      </c>
+      <c r="D364" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="E364" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="F364" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="G364" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H364" s="3" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="I364" t="s">
+        <v>30</v>
+      </c>
+      <c r="J364" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B365" t="s">
+        <v>161</v>
+      </c>
+      <c r="C365" t="s">
+        <v>168</v>
+      </c>
+      <c r="D365" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="E365" s="3" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="F365" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="G365" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H365" s="3" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="I365" t="s">
+        <v>30</v>
+      </c>
+      <c r="J365" t="s">
+        <v>217</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/indicator-performance-table.xlsx
+++ b/indicator-performance-table.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="221">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -666,6 +666,15 @@
   </si>
   <si>
     <t xml:space="preserve">However, trust in the NI Assembly was higher in 2025 than in 2022 and 2023. It was similar to 2024.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Over the last ten years, the proportion of individuals in absolute poverty (BHC) generally decreased slowly from a high of 21% in 2013/14 to a low of 12% in 2020/21 before increasing to the current position of 15% in 2023/24. Due to the ongoing transformation work to the Family Resources Survey (FRS) these figures remain subject to revision and may change in future releases. Further information on this transformation work is available &lt;a href = 'https://www.communities-ni.gov.uk/topics/family-resources-survey-and-poverty-analysis' target = '_blank'&gt;from this link. &lt;/a&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Over the last ten years, the proportion of individuals in relative poverty (BHC) has fluctuated between a high of 22% in 2014/15 and lows of 16% in 2017/18 and 2021/22. Due to the ongoing transformation work to the Family Resources Survey (FRS) these figures remain subject to revision and may change in future releases. Further information on this transformation work is available &lt;a href = 'https://www.communities-ni.gov.uk/topics/family-resources-survey-and-poverty-analysis' target = '_blank'&gt;from this link. &lt;/a&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Over the last ten years, the proportion of individuals in households spending 30% or more of household income on housing costs generally decreased slowly from a high of 11% in 2013/14 to a low of 6% in 2021/22. However, there has consistently been a larger proportion spending 30% or more of household income on housing costs in the rental sectors compared to the overall population. Due to the ongoing transformation work to the Family Resources Survey (FRS) these figures remain subject to revision and may change in future releases. Further information on this transformation work is available &lt;a href = 'https://www.communities-ni.gov.uk/topics/family-resources-survey-and-poverty-analysis' target = '_blank'&gt;from this link. &lt;/a&gt;</t>
   </si>
 </sst>
 </file>
@@ -11471,7 +11480,7 @@
         <v>30</v>
       </c>
       <c r="J328" t="s">
-        <v>70</v>
+        <v>218</v>
       </c>
     </row>
     <row r="329">
@@ -11503,7 +11512,7 @@
         <v>30</v>
       </c>
       <c r="J329" t="s">
-        <v>72</v>
+        <v>219</v>
       </c>
     </row>
     <row r="330">
@@ -12491,7 +12500,7 @@
         <v>30</v>
       </c>
       <c r="J360" t="s">
-        <v>158</v>
+        <v>220</v>
       </c>
     </row>
     <row r="361">

--- a/indicator-performance-table.xlsx
+++ b/indicator-performance-table.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="226">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -675,6 +675,21 @@
   </si>
   <si>
     <t xml:space="preserve">Over the last ten years, the proportion of individuals in households spending 30% or more of household income on housing costs generally decreased slowly from a high of 11% in 2013/14 to a low of 6% in 2021/22. However, there has consistently been a larger proportion spending 30% or more of household income on housing costs in the rental sectors compared to the overall population. Due to the ongoing transformation work to the Family Resources Survey (FRS) these figures remain subject to revision and may change in future releases. Further information on this transformation work is available &lt;a href = 'https://www.communities-ni.gov.uk/topics/family-resources-survey-and-poverty-analysis' target = '_blank'&gt;from this link. &lt;/a&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Over the last ten years, the proportion of individuals in absolute poverty (BHC) generally decreased slowly from a high of 21% in 2013/14 to a low of 12% in 2020/21 before increasing to the current position of 15% in 2023/24. Changes are being made to the way poverty and income statistics are produced in Northern Ireland to improve the quality, coherence and completeness of income-based poverty statistics. Consequently, the figures for this indicator are under review. The latest information and revised statistics are available &lt;a href = 'https://www.communities-ni.gov.uk/topics/family-resources-survey-and-poverty-analysis' target = '_blank'&gt;from this link. &lt;/a&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Over the last ten years, the proportion of individuals in relative poverty (BHC) has fluctuated between a high of 22% in 2014/15 and lows of 16% in 2017/18 and 2021/22. Changes are being made to the way poverty and income statistics are produced in Northern Ireland to improve the quality, coherence and completeness of income-based poverty statistics. Consequently, the figures for this indicator are under review. The latest information and revised statistics are available &lt;a href = 'https://www.communities-ni.gov.uk/topics/family-resources-survey-and-poverty-analysis' target = '_blank'&gt;from this link. &lt;/a&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Economic activity has increased gradually in recent years. Economic activity post-pandemic has recovered substantially and the latest 2025 data is now at a series high. Over the first quarter of 2026, economic output in Northern Ireland increased by 0.7%,  mainly driven by increased activity in the Services sector. Quarterly figures are available &lt;a href = 'https://www.nisra.gov.uk/statistics/economic-output-statistics/ni-composite-economic-index' target = '_blank'&gt;from this link. &lt;/a&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">From 2021/22 until 2023/24, the number of households accepted as homeless rose year on year. While the number of households accepted as homeless decreased in 2024/25 and remained similar to that lower level in 2025/26, it is still higher than the position in 2021/22. All of those who are accepted as statutorily homeless have a statutory duty to temporary accommodation and there has been an increase in the number of placements in temporary accommodation over the period, from 9,265 placements in 2021/22 to 12,739 in 2025/26. The number of households accepted as homeless is an annual total for each given year whereas the number of households placed in Temporary Accommodation is a cumulative figure that will include households that were accepted as homeless in previous years. Not all households accepted as homeless will be allocated a home within the same year. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Over the last ten years, the proportion of individuals in households spending 30% or more of household income on housing costs generally decreased slowly from a high of 11% in 2013/14 to a low of 6% in 2021/22. However, there has consistently been a larger proportion spending 30% or more of household income on housing costs in the rental sectors compared to the overall population. Changes are being made to the way poverty and income statistics are produced in Northern Ireland to improve the quality, coherence and completeness of income-based poverty statistics. Consequently, the figures for this indicator are under review. The latest information and revised statistics are available &lt;a href = 'https://www.communities-ni.gov.uk/topics/family-resources-survey-and-poverty-analysis' target = '_blank'&gt;from this link. &lt;/a&gt;</t>
   </si>
 </sst>
 </file>
@@ -734,8 +749,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:J365" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:J365"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:J417" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:J417"/>
   <tableColumns count="10">
     <tableColumn id="1" name="date"/>
     <tableColumn id="2" name="domain"/>
@@ -12663,6 +12678,1666 @@
         <v>217</v>
       </c>
     </row>
+    <row r="366">
+      <c r="A366" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B366" t="s">
+        <v>10</v>
+      </c>
+      <c r="C366" t="s">
+        <v>11</v>
+      </c>
+      <c r="D366" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E366" s="3" t="n">
+        <v>63</v>
+      </c>
+      <c r="F366" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G366" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H366" s="3" t="n">
+        <v>68</v>
+      </c>
+      <c r="I366" t="s">
+        <v>15</v>
+      </c>
+      <c r="J366" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B367" t="s">
+        <v>10</v>
+      </c>
+      <c r="C367" t="s">
+        <v>17</v>
+      </c>
+      <c r="D367" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E367" s="3" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="F367" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G367" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H367" s="3" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="I367" t="s">
+        <v>21</v>
+      </c>
+      <c r="J367" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B368" t="s">
+        <v>10</v>
+      </c>
+      <c r="C368" t="s">
+        <v>23</v>
+      </c>
+      <c r="D368" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E368" s="3" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="F368" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G368" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H368" s="3" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="I368" t="s">
+        <v>21</v>
+      </c>
+      <c r="J368" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B369" t="s">
+        <v>10</v>
+      </c>
+      <c r="C369" t="s">
+        <v>26</v>
+      </c>
+      <c r="D369" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E369" s="3" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="F369" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G369" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H369" s="3" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="I369" t="s">
+        <v>30</v>
+      </c>
+      <c r="J369" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B370" t="s">
+        <v>32</v>
+      </c>
+      <c r="C370" t="s">
+        <v>33</v>
+      </c>
+      <c r="D370" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E370" s="3" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="F370" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G370" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H370" s="3" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="I370" t="s">
+        <v>15</v>
+      </c>
+      <c r="J370" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B371" t="s">
+        <v>32</v>
+      </c>
+      <c r="C371" t="s">
+        <v>37</v>
+      </c>
+      <c r="D371" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E371" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="F371" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G371" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H371" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="I371" t="s">
+        <v>21</v>
+      </c>
+      <c r="J371" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B372" t="s">
+        <v>32</v>
+      </c>
+      <c r="C372" t="s">
+        <v>39</v>
+      </c>
+      <c r="D372" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E372" s="3" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="F372" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="G372" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="H372" s="3" t="n">
+        <v>52</v>
+      </c>
+      <c r="I372" t="s">
+        <v>21</v>
+      </c>
+      <c r="J372" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B373" t="s">
+        <v>32</v>
+      </c>
+      <c r="C373" t="s">
+        <v>44</v>
+      </c>
+      <c r="D373" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E373" s="3" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="F373" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G373" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H373" s="3" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="I373" t="s">
+        <v>15</v>
+      </c>
+      <c r="J373" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B374" t="s">
+        <v>32</v>
+      </c>
+      <c r="C374" t="s">
+        <v>47</v>
+      </c>
+      <c r="D374" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E374" s="3" t="n">
+        <v>48.2</v>
+      </c>
+      <c r="F374" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G374" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="H374" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="I374" t="s">
+        <v>21</v>
+      </c>
+      <c r="J374" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B375" t="s">
+        <v>32</v>
+      </c>
+      <c r="C375" t="s">
+        <v>50</v>
+      </c>
+      <c r="D375" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E375" s="3" t="n">
+        <v>51.9</v>
+      </c>
+      <c r="F375" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="G375" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H375" s="3" t="n">
+        <v>51</v>
+      </c>
+      <c r="I375" t="s">
+        <v>30</v>
+      </c>
+      <c r="J375" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B376" t="s">
+        <v>32</v>
+      </c>
+      <c r="C376" t="s">
+        <v>53</v>
+      </c>
+      <c r="D376" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="E376" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="F376" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="G376" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H376" s="3" t="n">
+        <v>47</v>
+      </c>
+      <c r="I376" t="s">
+        <v>15</v>
+      </c>
+      <c r="J376" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B377" t="s">
+        <v>32</v>
+      </c>
+      <c r="C377" t="s">
+        <v>56</v>
+      </c>
+      <c r="D377" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E377" s="3" t="n">
+        <v>0.063</v>
+      </c>
+      <c r="F377" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="G377" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H377" s="3" t="n">
+        <v>0.07</v>
+      </c>
+      <c r="I377" t="s">
+        <v>30</v>
+      </c>
+      <c r="J377" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B378" t="s">
+        <v>32</v>
+      </c>
+      <c r="C378" t="s">
+        <v>59</v>
+      </c>
+      <c r="D378" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E378" s="3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="F378" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="G378" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H378" s="3" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="I378" t="s">
+        <v>30</v>
+      </c>
+      <c r="J378" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B379" t="s">
+        <v>63</v>
+      </c>
+      <c r="C379" t="s">
+        <v>64</v>
+      </c>
+      <c r="D379" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E379" s="3" t="n">
+        <v>49.6</v>
+      </c>
+      <c r="F379" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="G379" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H379" s="3" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="I379" t="s">
+        <v>15</v>
+      </c>
+      <c r="J379" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B380" t="s">
+        <v>63</v>
+      </c>
+      <c r="C380" t="s">
+        <v>67</v>
+      </c>
+      <c r="D380" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E380" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="F380" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="G380" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="H380" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="I380" t="s">
+        <v>30</v>
+      </c>
+      <c r="J380" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B381" t="s">
+        <v>63</v>
+      </c>
+      <c r="C381" t="s">
+        <v>71</v>
+      </c>
+      <c r="D381" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E381" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="F381" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="G381" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="H381" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="I381" t="s">
+        <v>30</v>
+      </c>
+      <c r="J381" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B382" t="s">
+        <v>63</v>
+      </c>
+      <c r="C382" t="s">
+        <v>73</v>
+      </c>
+      <c r="D382" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E382" s="3" t="n">
+        <v>36.1</v>
+      </c>
+      <c r="F382" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="G382" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H382" s="3" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="I382" t="s">
+        <v>21</v>
+      </c>
+      <c r="J382" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B383" t="s">
+        <v>75</v>
+      </c>
+      <c r="C383" t="s">
+        <v>76</v>
+      </c>
+      <c r="D383" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E383" s="3" t="n">
+        <v>56</v>
+      </c>
+      <c r="F383" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="G383" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H383" s="3" t="n">
+        <v>56.3</v>
+      </c>
+      <c r="I383" t="s">
+        <v>30</v>
+      </c>
+      <c r="J383" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B384" t="s">
+        <v>75</v>
+      </c>
+      <c r="C384" t="s">
+        <v>78</v>
+      </c>
+      <c r="D384" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="E384" s="3" t="n">
+        <v>62.1</v>
+      </c>
+      <c r="F384" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="G384" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="H384" s="3" t="n">
+        <v>60.2</v>
+      </c>
+      <c r="I384" t="s">
+        <v>21</v>
+      </c>
+      <c r="J384" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B385" t="s">
+        <v>75</v>
+      </c>
+      <c r="C385" t="s">
+        <v>83</v>
+      </c>
+      <c r="D385" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="E385" s="3" t="n">
+        <v>60.1</v>
+      </c>
+      <c r="F385" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="G385" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="H385" s="3" t="n">
+        <v>59.3</v>
+      </c>
+      <c r="I385" t="s">
+        <v>30</v>
+      </c>
+      <c r="J385" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B386" t="s">
+        <v>75</v>
+      </c>
+      <c r="C386" t="s">
+        <v>86</v>
+      </c>
+      <c r="D386" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E386" s="3" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="F386" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="G386" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H386" s="3" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="I386" t="s">
+        <v>15</v>
+      </c>
+      <c r="J386" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B387" t="s">
+        <v>75</v>
+      </c>
+      <c r="C387" t="s">
+        <v>89</v>
+      </c>
+      <c r="D387" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="E387" s="3" t="n">
+        <v>173</v>
+      </c>
+      <c r="F387" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="G387" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="H387" s="3" t="n">
+        <v>181</v>
+      </c>
+      <c r="I387" t="s">
+        <v>21</v>
+      </c>
+      <c r="J387" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B388" t="s">
+        <v>75</v>
+      </c>
+      <c r="C388" t="s">
+        <v>94</v>
+      </c>
+      <c r="D388" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E388" s="3" t="n">
+        <v>75</v>
+      </c>
+      <c r="F388" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="G388" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H388" s="3" t="n">
+        <v>73</v>
+      </c>
+      <c r="I388" t="s">
+        <v>21</v>
+      </c>
+      <c r="J388" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B389" t="s">
+        <v>98</v>
+      </c>
+      <c r="C389" t="s">
+        <v>99</v>
+      </c>
+      <c r="D389" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E389" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="F389" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="G389" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H389" s="3" t="n">
+        <v>85</v>
+      </c>
+      <c r="I389" t="s">
+        <v>15</v>
+      </c>
+      <c r="J389" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B390" t="s">
+        <v>98</v>
+      </c>
+      <c r="C390" t="s">
+        <v>101</v>
+      </c>
+      <c r="D390" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E390" s="3" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="F390" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="G390" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H390" s="3" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="I390" t="s">
+        <v>30</v>
+      </c>
+      <c r="J390" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B391" t="s">
+        <v>98</v>
+      </c>
+      <c r="C391" t="s">
+        <v>104</v>
+      </c>
+      <c r="D391" s="3"/>
+      <c r="E391" s="3"/>
+      <c r="F391" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="G391" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H391" s="3" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="I391" t="s">
+        <v>61</v>
+      </c>
+      <c r="J391" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B392" t="s">
+        <v>98</v>
+      </c>
+      <c r="C392" t="s">
+        <v>106</v>
+      </c>
+      <c r="D392" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E392" s="3" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="F392" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="G392" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H392" s="3" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="I392" t="s">
+        <v>21</v>
+      </c>
+      <c r="J392" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B393" t="s">
+        <v>108</v>
+      </c>
+      <c r="C393" t="s">
+        <v>109</v>
+      </c>
+      <c r="D393" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E393" s="3" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="F393" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="G393" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H393" s="3" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="I393" t="s">
+        <v>15</v>
+      </c>
+      <c r="J393" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B394" t="s">
+        <v>108</v>
+      </c>
+      <c r="C394" t="s">
+        <v>111</v>
+      </c>
+      <c r="D394" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E394" s="3" t="n">
+        <v>69.8</v>
+      </c>
+      <c r="F394" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="G394" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H394" s="3" t="n">
+        <v>74.3</v>
+      </c>
+      <c r="I394" t="s">
+        <v>15</v>
+      </c>
+      <c r="J394" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B395" t="s">
+        <v>108</v>
+      </c>
+      <c r="C395" t="s">
+        <v>114</v>
+      </c>
+      <c r="D395" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E395" s="3" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="F395" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="G395" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H395" s="3" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="I395" t="s">
+        <v>15</v>
+      </c>
+      <c r="J395" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B396" t="s">
+        <v>108</v>
+      </c>
+      <c r="C396" t="s">
+        <v>117</v>
+      </c>
+      <c r="D396" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="E396" s="3" t="n">
+        <v>66.9</v>
+      </c>
+      <c r="F396" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="G396" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H396" s="3" t="n">
+        <v>69</v>
+      </c>
+      <c r="I396" t="s">
+        <v>15</v>
+      </c>
+      <c r="J396" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B397" t="s">
+        <v>108</v>
+      </c>
+      <c r="C397" t="s">
+        <v>119</v>
+      </c>
+      <c r="D397" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="E397" s="3" t="n">
+        <v>61.27</v>
+      </c>
+      <c r="F397" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G397" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H397" s="3" t="n">
+        <v>62.21</v>
+      </c>
+      <c r="I397" t="s">
+        <v>30</v>
+      </c>
+      <c r="J397" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B398" t="s">
+        <v>108</v>
+      </c>
+      <c r="C398" t="s">
+        <v>121</v>
+      </c>
+      <c r="D398" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E398" s="3" t="n">
+        <v>92.8</v>
+      </c>
+      <c r="F398" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G398" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H398" s="3" t="n">
+        <v>99.5</v>
+      </c>
+      <c r="I398" t="s">
+        <v>15</v>
+      </c>
+      <c r="J398" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B399" t="s">
+        <v>108</v>
+      </c>
+      <c r="C399" t="s">
+        <v>123</v>
+      </c>
+      <c r="D399" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="E399" s="3" t="n">
+        <v>96.3</v>
+      </c>
+      <c r="F399" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G399" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H399" s="3" t="n">
+        <v>104.1</v>
+      </c>
+      <c r="I399" t="s">
+        <v>15</v>
+      </c>
+      <c r="J399" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B400" t="s">
+        <v>108</v>
+      </c>
+      <c r="C400" t="s">
+        <v>126</v>
+      </c>
+      <c r="D400" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E400" s="3" t="n">
+        <v>1170.4</v>
+      </c>
+      <c r="F400" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G400" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H400" s="3" t="n">
+        <v>1000.7</v>
+      </c>
+      <c r="I400" t="s">
+        <v>21</v>
+      </c>
+      <c r="J400" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B401" t="s">
+        <v>108</v>
+      </c>
+      <c r="C401" t="s">
+        <v>128</v>
+      </c>
+      <c r="D401" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E401" s="3" t="n">
+        <v>76.3</v>
+      </c>
+      <c r="F401" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="G401" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H401" s="3" t="n">
+        <v>80.4</v>
+      </c>
+      <c r="I401" t="s">
+        <v>15</v>
+      </c>
+      <c r="J401" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B402" t="s">
+        <v>131</v>
+      </c>
+      <c r="C402" t="s">
+        <v>132</v>
+      </c>
+      <c r="D402" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E402" s="3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="F402" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="G402" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="H402" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I402" t="s">
+        <v>30</v>
+      </c>
+      <c r="J402" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B403" t="s">
+        <v>131</v>
+      </c>
+      <c r="C403" t="s">
+        <v>134</v>
+      </c>
+      <c r="D403" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E403" s="3" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="F403" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="G403" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="H403" s="3" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="I403" t="s">
+        <v>30</v>
+      </c>
+      <c r="J403" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B404" t="s">
+        <v>131</v>
+      </c>
+      <c r="C404" t="s">
+        <v>136</v>
+      </c>
+      <c r="D404" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="E404" s="3" t="n">
+        <v>193</v>
+      </c>
+      <c r="F404" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="G404" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H404" s="3" t="n">
+        <v>189</v>
+      </c>
+      <c r="I404" t="s">
+        <v>30</v>
+      </c>
+      <c r="J404" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B405" t="s">
+        <v>131</v>
+      </c>
+      <c r="C405" t="s">
+        <v>140</v>
+      </c>
+      <c r="D405" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E405" s="3" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="F405" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="G405" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H405" s="3" t="n">
+        <v>40.7</v>
+      </c>
+      <c r="I405" t="s">
+        <v>21</v>
+      </c>
+      <c r="J405" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B406" t="s">
+        <v>131</v>
+      </c>
+      <c r="C406" t="s">
+        <v>142</v>
+      </c>
+      <c r="D406" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E406" s="3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="F406" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="G406" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="H406" s="3" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="I406" t="s">
+        <v>30</v>
+      </c>
+      <c r="J406" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B407" t="s">
+        <v>145</v>
+      </c>
+      <c r="C407" t="s">
+        <v>146</v>
+      </c>
+      <c r="D407" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E407" s="3" t="n">
+        <v>68.4</v>
+      </c>
+      <c r="F407" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G407" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H407" s="3" t="n">
+        <v>69.2</v>
+      </c>
+      <c r="I407" t="s">
+        <v>30</v>
+      </c>
+      <c r="J407" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B408" t="s">
+        <v>145</v>
+      </c>
+      <c r="C408" t="s">
+        <v>148</v>
+      </c>
+      <c r="D408" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E408" s="3" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="F408" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="G408" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H408" s="3" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="I408" t="s">
+        <v>15</v>
+      </c>
+      <c r="J408" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B409" t="s">
+        <v>145</v>
+      </c>
+      <c r="C409" t="s">
+        <v>150</v>
+      </c>
+      <c r="D409" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="E409" s="3" t="n">
+        <v>47</v>
+      </c>
+      <c r="F409" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="G409" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H409" s="3" t="n">
+        <v>46</v>
+      </c>
+      <c r="I409" t="s">
+        <v>30</v>
+      </c>
+      <c r="J409" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B410" t="s">
+        <v>152</v>
+      </c>
+      <c r="C410" t="s">
+        <v>153</v>
+      </c>
+      <c r="D410" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E410" s="3" t="n">
+        <v>90</v>
+      </c>
+      <c r="F410" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="G410" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H410" s="3" t="n">
+        <v>91</v>
+      </c>
+      <c r="I410" t="s">
+        <v>30</v>
+      </c>
+      <c r="J410" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B411" t="s">
+        <v>152</v>
+      </c>
+      <c r="C411" t="s">
+        <v>154</v>
+      </c>
+      <c r="D411" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E411" s="3" t="n">
+        <v>10135</v>
+      </c>
+      <c r="F411" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="G411" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="H411" s="3" t="n">
+        <v>10852</v>
+      </c>
+      <c r="I411" t="s">
+        <v>21</v>
+      </c>
+      <c r="J411" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B412" t="s">
+        <v>152</v>
+      </c>
+      <c r="C412" t="s">
+        <v>156</v>
+      </c>
+      <c r="D412" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E412" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F412" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="G412" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="H412" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="I412" t="s">
+        <v>30</v>
+      </c>
+      <c r="J412" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B413" t="s">
+        <v>152</v>
+      </c>
+      <c r="C413" t="s">
+        <v>159</v>
+      </c>
+      <c r="D413" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E413" s="3" t="n">
+        <v>31407</v>
+      </c>
+      <c r="F413" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="G413" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="H413" s="3" t="n">
+        <v>39008</v>
+      </c>
+      <c r="I413" t="s">
+        <v>21</v>
+      </c>
+      <c r="J413" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B414" t="s">
+        <v>161</v>
+      </c>
+      <c r="C414" t="s">
+        <v>162</v>
+      </c>
+      <c r="D414" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E414" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="F414" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="G414" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H414" s="3" t="n">
+        <v>46.7</v>
+      </c>
+      <c r="I414" t="s">
+        <v>15</v>
+      </c>
+      <c r="J414" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B415" t="s">
+        <v>161</v>
+      </c>
+      <c r="C415" t="s">
+        <v>164</v>
+      </c>
+      <c r="D415" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E415" s="3" t="n">
+        <v>78.6</v>
+      </c>
+      <c r="F415" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="G415" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H415" s="3" t="n">
+        <v>76.1</v>
+      </c>
+      <c r="I415" t="s">
+        <v>21</v>
+      </c>
+      <c r="J415" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B416" t="s">
+        <v>161</v>
+      </c>
+      <c r="C416" t="s">
+        <v>165</v>
+      </c>
+      <c r="D416" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="E416" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="F416" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="G416" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H416" s="3" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="I416" t="s">
+        <v>30</v>
+      </c>
+      <c r="J416" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B417" t="s">
+        <v>161</v>
+      </c>
+      <c r="C417" t="s">
+        <v>168</v>
+      </c>
+      <c r="D417" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="E417" s="3" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="F417" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="G417" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H417" s="3" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="I417" t="s">
+        <v>30</v>
+      </c>
+      <c r="J417" t="s">
+        <v>217</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
